--- a/data/task_parameters_evaluation.xlsx
+++ b/data/task_parameters_evaluation.xlsx
@@ -458,7 +458,7 @@
         <v>5.662996678308536</v>
       </c>
       <c r="C2" t="n">
-        <v>551594014.0339438</v>
+        <v>2041275211.227155</v>
       </c>
       <c r="D2" t="n">
         <v>0.999</v>
@@ -472,7 +472,7 @@
         <v>6.934746584869963</v>
       </c>
       <c r="C3" t="n">
-        <v>1360423102.866345</v>
+        <v>2688338482.293077</v>
       </c>
       <c r="D3" t="n">
         <v>0.999</v>
@@ -486,7 +486,7 @@
         <v>9.57515642366312</v>
       </c>
       <c r="C4" t="n">
-        <v>754255959.3572752</v>
+        <v>2203404767.48582</v>
       </c>
       <c r="D4" t="n">
         <v>0.9999</v>
@@ -500,7 +500,7 @@
         <v>7.830633241004661</v>
       </c>
       <c r="C5" t="n">
-        <v>2669617705.232189</v>
+        <v>3735694164.185751</v>
       </c>
       <c r="D5" t="n">
         <v>0.999</v>
@@ -514,7 +514,7 @@
         <v>6.948133034682074</v>
       </c>
       <c r="C6" t="n">
-        <v>800697920.804878</v>
+        <v>2240558336.643902</v>
       </c>
       <c r="D6" t="n">
         <v>0.9</v>
@@ -528,7 +528,7 @@
         <v>8.297325461549779</v>
       </c>
       <c r="C7" t="n">
-        <v>2004984629.905189</v>
+        <v>3203987703.924151</v>
       </c>
       <c r="D7" t="n">
         <v>0.9</v>
@@ -542,7 +542,7 @@
         <v>6.198463480157266</v>
       </c>
       <c r="C8" t="n">
-        <v>2292413282.842319</v>
+        <v>3433930626.273855</v>
       </c>
       <c r="D8" t="n">
         <v>0.9</v>
@@ -556,7 +556,7 @@
         <v>6.96042089223903</v>
       </c>
       <c r="C9" t="n">
-        <v>2212841786.664807</v>
+        <v>3370273429.331845</v>
       </c>
       <c r="D9" t="n">
         <v>0.99</v>
@@ -570,7 +570,7 @@
         <v>5.977398207811014</v>
       </c>
       <c r="C10" t="n">
-        <v>2016086250.954767</v>
+        <v>3212869000.763814</v>
       </c>
       <c r="D10" t="n">
         <v>0.9999</v>
@@ -584,7 +584,7 @@
         <v>6.553330529404843</v>
       </c>
       <c r="C11" t="n">
-        <v>1448779386.945152</v>
+        <v>2759023509.556121</v>
       </c>
       <c r="D11" t="n">
         <v>0.9</v>
@@ -598,7 +598,7 @@
         <v>9.837669013985309</v>
       </c>
       <c r="C12" t="n">
-        <v>2549908466.263318</v>
+        <v>3639926773.010654</v>
       </c>
       <c r="D12" t="n">
         <v>0.9999</v>
@@ -612,7 +612,7 @@
         <v>8.558726743559294</v>
       </c>
       <c r="C13" t="n">
-        <v>1563434931.549369</v>
+        <v>2850747945.239495</v>
       </c>
       <c r="D13" t="n">
         <v>0.9999</v>
@@ -626,7 +626,7 @@
         <v>5.02775854023147</v>
       </c>
       <c r="C14" t="n">
-        <v>1750501054.790796</v>
+        <v>3000400843.832637</v>
       </c>
       <c r="D14" t="n">
         <v>0.99</v>
@@ -640,7 +640,7 @@
         <v>5.980188509284573</v>
       </c>
       <c r="C15" t="n">
-        <v>2100984893.149724</v>
+        <v>3280787914.51978</v>
       </c>
       <c r="D15" t="n">
         <v>0.99</v>
@@ -654,7 +654,7 @@
         <v>5.728458854750012</v>
       </c>
       <c r="C16" t="n">
-        <v>2639410809.481323</v>
+        <v>3711528647.585059</v>
       </c>
       <c r="D16" t="n">
         <v>0.9999</v>
@@ -668,7 +668,7 @@
         <v>9.449430795250247</v>
       </c>
       <c r="C17" t="n">
-        <v>1883026220.969368</v>
+        <v>3106420976.775494</v>
       </c>
       <c r="D17" t="n">
         <v>0.999</v>
@@ -682,7 +682,7 @@
         <v>8.939792606571656</v>
       </c>
       <c r="C18" t="n">
-        <v>595130042.9857408</v>
+        <v>2076104034.388592</v>
       </c>
       <c r="D18" t="n">
         <v>0.9</v>
@@ -696,7 +696,7 @@
         <v>9.135768591784299</v>
       </c>
       <c r="C19" t="n">
-        <v>2342246368.103442</v>
+        <v>3473797094.482754</v>
       </c>
       <c r="D19" t="n">
         <v>0.99</v>
@@ -710,7 +710,7 @@
         <v>5.375396312241319</v>
       </c>
       <c r="C20" t="n">
-        <v>545053860.8204573</v>
+        <v>2036043088.656366</v>
       </c>
       <c r="D20" t="n">
         <v>0.9999</v>
@@ -724,7 +724,7 @@
         <v>5.523217206683926</v>
       </c>
       <c r="C21" t="n">
-        <v>1447330628.843225</v>
+        <v>2757864503.07458</v>
       </c>
       <c r="D21" t="n">
         <v>0.99</v>
@@ -738,7 +738,7 @@
         <v>6.457134101567848</v>
       </c>
       <c r="C22" t="n">
-        <v>987405396.9111412</v>
+        <v>2389924317.528913</v>
       </c>
       <c r="D22" t="n">
         <v>0.9999</v>
@@ -752,7 +752,7 @@
         <v>7.193823660493466</v>
       </c>
       <c r="C23" t="n">
-        <v>541182008.1358924</v>
+        <v>2032945606.508714</v>
       </c>
       <c r="D23" t="n">
         <v>0.999</v>
@@ -766,7 +766,7 @@
         <v>6.791170179457382</v>
       </c>
       <c r="C24" t="n">
-        <v>824581456.499877</v>
+        <v>2259665165.199902</v>
       </c>
       <c r="D24" t="n">
         <v>0.9999</v>
@@ -780,7 +780,7 @@
         <v>5.835354536183841</v>
       </c>
       <c r="C25" t="n">
-        <v>1522193296.544004</v>
+        <v>2817754637.235204</v>
       </c>
       <c r="D25" t="n">
         <v>0.9</v>
@@ -794,7 +794,7 @@
         <v>7.859058306008071</v>
       </c>
       <c r="C26" t="n">
-        <v>1020011320.737263</v>
+        <v>2416009056.58981</v>
       </c>
       <c r="D26" t="n">
         <v>0.9</v>
@@ -808,7 +808,7 @@
         <v>9.041206839833173</v>
       </c>
       <c r="C27" t="n">
-        <v>2799112326.882765</v>
+        <v>3839289861.506212</v>
       </c>
       <c r="D27" t="n">
         <v>0.9999</v>
@@ -822,7 +822,7 @@
         <v>6.561628659759453</v>
       </c>
       <c r="C28" t="n">
-        <v>2511236054.135225</v>
+        <v>3608988843.308181</v>
       </c>
       <c r="D28" t="n">
         <v>0.9</v>
@@ -836,7 +836,7 @@
         <v>7.617204269308933</v>
       </c>
       <c r="C29" t="n">
-        <v>2923615745.961377</v>
+        <v>3938892596.769102</v>
       </c>
       <c r="D29" t="n">
         <v>0.99</v>
@@ -850,7 +850,7 @@
         <v>5.650853201497548</v>
       </c>
       <c r="C30" t="n">
-        <v>2961998229.458154</v>
+        <v>3969598583.566524</v>
       </c>
       <c r="D30" t="n">
         <v>0.99</v>
@@ -864,7 +864,7 @@
         <v>9.433470292635988</v>
       </c>
       <c r="C31" t="n">
-        <v>2675098031.560039</v>
+        <v>3740078425.248031</v>
       </c>
       <c r="D31" t="n">
         <v>0.99</v>
@@ -878,7 +878,7 @@
         <v>8.559263164073792</v>
       </c>
       <c r="C32" t="n">
-        <v>2110879957.314068</v>
+        <v>3288703965.851254</v>
       </c>
       <c r="D32" t="n">
         <v>0.9999</v>
@@ -892,7 +892,7 @@
         <v>6.226322674160651</v>
       </c>
       <c r="C33" t="n">
-        <v>2843347453.316847</v>
+        <v>3874677962.653478</v>
       </c>
       <c r="D33" t="n">
         <v>0.9999</v>
@@ -906,7 +906,7 @@
         <v>6.184261579741684</v>
       </c>
       <c r="C34" t="n">
-        <v>2483910662.127912</v>
+        <v>3587128529.70233</v>
       </c>
       <c r="D34" t="n">
         <v>0.99</v>
@@ -920,7 +920,7 @@
         <v>7.954441681736775</v>
       </c>
       <c r="C35" t="n">
-        <v>1188482382.850053</v>
+        <v>2550785906.280042</v>
       </c>
       <c r="D35" t="n">
         <v>0.9999</v>
@@ -934,7 +934,7 @@
         <v>8.989368429787117</v>
       </c>
       <c r="C36" t="n">
-        <v>1834272571.430021</v>
+        <v>3067418057.144017</v>
       </c>
       <c r="D36" t="n">
         <v>0.999</v>
@@ -948,7 +948,7 @@
         <v>6.88996346336233</v>
       </c>
       <c r="C37" t="n">
-        <v>2937366093.442816</v>
+        <v>3949892874.754253</v>
       </c>
       <c r="D37" t="n">
         <v>0.99</v>
@@ -962,7 +962,7 @@
         <v>6.20059831376159</v>
       </c>
       <c r="C38" t="n">
-        <v>1195900611.64841</v>
+        <v>2556720489.318728</v>
       </c>
       <c r="D38" t="n">
         <v>0.9999</v>
@@ -976,7 +976,7 @@
         <v>7.809635425850978</v>
       </c>
       <c r="C39" t="n">
-        <v>1963355568.788111</v>
+        <v>3170684455.030489</v>
       </c>
       <c r="D39" t="n">
         <v>0.99</v>
@@ -990,7 +990,7 @@
         <v>6.790193362807514</v>
       </c>
       <c r="C40" t="n">
-        <v>1376073726.702605</v>
+        <v>2700858981.362084</v>
       </c>
       <c r="D40" t="n">
         <v>0.999</v>
@@ -1004,7 +1004,7 @@
         <v>5.060161821432336</v>
       </c>
       <c r="C41" t="n">
-        <v>1894874666.182604</v>
+        <v>3115899732.946083</v>
       </c>
       <c r="D41" t="n">
         <v>0.9</v>
@@ -1018,7 +1018,7 @@
         <v>6.201712270413927</v>
       </c>
       <c r="C42" t="n">
-        <v>601269883.2496367</v>
+        <v>2081015906.599709</v>
       </c>
       <c r="D42" t="n">
         <v>0.9999</v>
@@ -1032,7 +1032,7 @@
         <v>7.48370010222253</v>
       </c>
       <c r="C43" t="n">
-        <v>1279986511.256631</v>
+        <v>2623989209.005305</v>
       </c>
       <c r="D43" t="n">
         <v>0.999</v>
@@ -1046,7 +1046,7 @@
         <v>8.181871452880136</v>
       </c>
       <c r="C44" t="n">
-        <v>1122165516.188407</v>
+        <v>2497732412.950726</v>
       </c>
       <c r="D44" t="n">
         <v>0.9999</v>
@@ -1060,7 +1060,7 @@
         <v>9.894431810705976</v>
       </c>
       <c r="C45" t="n">
-        <v>1853240764.44137</v>
+        <v>3082592611.553096</v>
       </c>
       <c r="D45" t="n">
         <v>0.9999</v>
@@ -1074,7 +1074,7 @@
         <v>9.84565734840081</v>
       </c>
       <c r="C46" t="n">
-        <v>1991486374.666785</v>
+        <v>3193189099.733428</v>
       </c>
       <c r="D46" t="n">
         <v>0.9</v>
@@ -1088,7 +1088,7 @@
         <v>7.424447859552025</v>
       </c>
       <c r="C47" t="n">
-        <v>2833420507.604648</v>
+        <v>3866736406.083718</v>
       </c>
       <c r="D47" t="n">
         <v>0.999</v>
@@ -1102,7 +1102,7 @@
         <v>9.82042276159355</v>
       </c>
       <c r="C48" t="n">
-        <v>2950680281.991236</v>
+        <v>3960544225.592988</v>
       </c>
       <c r="D48" t="n">
         <v>0.9</v>
@@ -1116,7 +1116,7 @@
         <v>9.821648577805249</v>
       </c>
       <c r="C49" t="n">
-        <v>1676503581.546941</v>
+        <v>2941202865.237553</v>
       </c>
       <c r="D49" t="n">
         <v>0.999</v>
@@ -1130,7 +1130,7 @@
         <v>7.507980308527412</v>
       </c>
       <c r="C50" t="n">
-        <v>1427492266.361013</v>
+        <v>2741993813.088811</v>
       </c>
       <c r="D50" t="n">
         <v>0.9999</v>
@@ -1144,7 +1144,7 @@
         <v>5.77377769302813</v>
       </c>
       <c r="C51" t="n">
-        <v>1716607789.574243</v>
+        <v>2973286231.659394</v>
       </c>
       <c r="D51" t="n">
         <v>0.9</v>
@@ -1158,7 +1158,7 @@
         <v>8.277420647584083</v>
       </c>
       <c r="C52" t="n">
-        <v>2878713187.646548</v>
+        <v>3902970550.117238</v>
       </c>
       <c r="D52" t="n">
         <v>0.99</v>
@@ -1172,7 +1172,7 @@
         <v>9.392196004864148</v>
       </c>
       <c r="C53" t="n">
-        <v>931552032.079576</v>
+        <v>2345241625.663661</v>
       </c>
       <c r="D53" t="n">
         <v>0.99</v>
@@ -1186,7 +1186,7 @@
         <v>5.607625083703032</v>
       </c>
       <c r="C54" t="n">
-        <v>965934350.6138394</v>
+        <v>2372747480.491072</v>
       </c>
       <c r="D54" t="n">
         <v>0.99</v>
@@ -1200,7 +1200,7 @@
         <v>5.762571890112357</v>
       </c>
       <c r="C55" t="n">
-        <v>1545126779.564868</v>
+        <v>2836101423.651895</v>
       </c>
       <c r="D55" t="n">
         <v>0.999</v>
@@ -1214,7 +1214,7 @@
         <v>8.878853582452443</v>
       </c>
       <c r="C56" t="n">
-        <v>2826440089.412699</v>
+        <v>3861152071.530159</v>
       </c>
       <c r="D56" t="n">
         <v>0.999</v>
@@ -1228,7 +1228,7 @@
         <v>5.186316931079313</v>
       </c>
       <c r="C57" t="n">
-        <v>1023465743.215471</v>
+        <v>2418772594.572377</v>
       </c>
       <c r="D57" t="n">
         <v>0.99</v>
@@ -1242,7 +1242,7 @@
         <v>7.209826266097405</v>
       </c>
       <c r="C58" t="n">
-        <v>610626119.4358729</v>
+        <v>2088500895.548698</v>
       </c>
       <c r="D58" t="n">
         <v>0.99</v>
@@ -1256,7 +1256,7 @@
         <v>8.681510758920858</v>
       </c>
       <c r="C59" t="n">
-        <v>816558732.7094724</v>
+        <v>2253246986.167578</v>
       </c>
       <c r="D59" t="n">
         <v>0.9</v>
@@ -1270,7 +1270,7 @@
         <v>7.038682262918668</v>
       </c>
       <c r="C60" t="n">
-        <v>1244497234.882042</v>
+        <v>2595597787.905633</v>
       </c>
       <c r="D60" t="n">
         <v>0.9999</v>
@@ -1284,7 +1284,7 @@
         <v>7.799179677544926</v>
       </c>
       <c r="C61" t="n">
-        <v>1515336991.990252</v>
+        <v>2812269593.592202</v>
       </c>
       <c r="D61" t="n">
         <v>0.9999</v>
@@ -1298,7 +1298,7 @@
         <v>9.319921075572854</v>
       </c>
       <c r="C62" t="n">
-        <v>2782846544.996487</v>
+        <v>3826277235.99719</v>
       </c>
       <c r="D62" t="n">
         <v>0.9999</v>
@@ -1312,7 +1312,7 @@
         <v>7.772879452695494</v>
       </c>
       <c r="C63" t="n">
-        <v>1226385704.274612</v>
+        <v>2581108563.41969</v>
       </c>
       <c r="D63" t="n">
         <v>0.9999</v>
@@ -1326,7 +1326,7 @@
         <v>9.358566469534704</v>
       </c>
       <c r="C64" t="n">
-        <v>1495628025.636365</v>
+        <v>2796502420.509092</v>
       </c>
       <c r="D64" t="n">
         <v>0.9999</v>
@@ -1340,7 +1340,7 @@
         <v>8.957534452301031</v>
       </c>
       <c r="C65" t="n">
-        <v>1412776876.972143</v>
+        <v>2730221501.577714</v>
       </c>
       <c r="D65" t="n">
         <v>0.99</v>
@@ -1354,7 +1354,7 @@
         <v>5.506834961082902</v>
       </c>
       <c r="C66" t="n">
-        <v>2818909396.054137</v>
+        <v>3855127516.843309</v>
       </c>
       <c r="D66" t="n">
         <v>0.9</v>
@@ -1368,7 +1368,7 @@
         <v>6.794097040679503</v>
       </c>
       <c r="C67" t="n">
-        <v>1252709965.649968</v>
+        <v>2602167972.519974</v>
       </c>
       <c r="D67" t="n">
         <v>0.9</v>
@@ -1382,7 +1382,7 @@
         <v>6.040411115495745</v>
       </c>
       <c r="C68" t="n">
-        <v>2910106228.831053</v>
+        <v>3928084983.064842</v>
       </c>
       <c r="D68" t="n">
         <v>0.99</v>
@@ -1396,7 +1396,7 @@
         <v>9.641488666250531</v>
       </c>
       <c r="C69" t="n">
-        <v>1166896056.540875</v>
+        <v>2533516845.2327</v>
       </c>
       <c r="D69" t="n">
         <v>0.99</v>
@@ -1410,7 +1410,7 @@
         <v>9.853842994059804</v>
       </c>
       <c r="C70" t="n">
-        <v>2718386409.159801</v>
+        <v>3774709127.327841</v>
       </c>
       <c r="D70" t="n">
         <v>0.999</v>
@@ -1424,7 +1424,7 @@
         <v>8.020365660718619</v>
       </c>
       <c r="C71" t="n">
-        <v>949481301.3165822</v>
+        <v>2359585041.053266</v>
       </c>
       <c r="D71" t="n">
         <v>0.99</v>
@@ -1438,7 +1438,7 @@
         <v>5.423139582333053</v>
       </c>
       <c r="C72" t="n">
-        <v>2873834889.833616</v>
+        <v>3899067911.866893</v>
       </c>
       <c r="D72" t="n">
         <v>0.999</v>
@@ -1452,7 +1452,7 @@
         <v>5.071335982192617</v>
       </c>
       <c r="C73" t="n">
-        <v>659921566.3855785</v>
+        <v>2127937253.108463</v>
       </c>
       <c r="D73" t="n">
         <v>0.9</v>
@@ -1466,7 +1466,7 @@
         <v>7.062618863539202</v>
       </c>
       <c r="C74" t="n">
-        <v>2352848551.684433</v>
+        <v>3482278841.347547</v>
       </c>
       <c r="D74" t="n">
         <v>0.99</v>
@@ -1480,7 +1480,7 @@
         <v>8.864275511896812</v>
       </c>
       <c r="C75" t="n">
-        <v>1615936667.269797</v>
+        <v>2892749333.815838</v>
       </c>
       <c r="D75" t="n">
         <v>0.9</v>
@@ -1494,7 +1494,7 @@
         <v>5.773437874803044</v>
       </c>
       <c r="C76" t="n">
-        <v>933716301.344082</v>
+        <v>2346973041.075265</v>
       </c>
       <c r="D76" t="n">
         <v>0.999</v>
@@ -1508,7 +1508,7 @@
         <v>6.637261253836789</v>
       </c>
       <c r="C77" t="n">
-        <v>1238761889.023338</v>
+        <v>2591009511.21867</v>
       </c>
       <c r="D77" t="n">
         <v>0.9999</v>
@@ -1522,7 +1522,7 @@
         <v>9.134283428823146</v>
       </c>
       <c r="C78" t="n">
-        <v>1951825999.153762</v>
+        <v>3161460799.323009</v>
       </c>
       <c r="D78" t="n">
         <v>0.9</v>
@@ -1536,7 +1536,7 @@
         <v>5.100649122647743</v>
       </c>
       <c r="C79" t="n">
-        <v>2104959870.640935</v>
+        <v>3283967896.512748</v>
       </c>
       <c r="D79" t="n">
         <v>0.99</v>
@@ -1550,7 +1550,7 @@
         <v>5.954222579723933</v>
       </c>
       <c r="C80" t="n">
-        <v>2346391606.574769</v>
+        <v>3477113285.259815</v>
       </c>
       <c r="D80" t="n">
         <v>0.9999</v>
@@ -1564,7 +1564,7 @@
         <v>7.333560944406281</v>
       </c>
       <c r="C81" t="n">
-        <v>1107119299.673279</v>
+        <v>2485695439.738623</v>
       </c>
       <c r="D81" t="n">
         <v>0.999</v>
@@ -1578,7 +1578,7 @@
         <v>5.476691071375097</v>
       </c>
       <c r="C82" t="n">
-        <v>2815529956.127483</v>
+        <v>3852423964.901986</v>
       </c>
       <c r="D82" t="n">
         <v>0.999</v>
@@ -1592,7 +1592,7 @@
         <v>7.511429282096248</v>
       </c>
       <c r="C83" t="n">
-        <v>2044687727.733188</v>
+        <v>3235750182.18655</v>
       </c>
       <c r="D83" t="n">
         <v>0.99</v>
@@ -1606,7 +1606,7 @@
         <v>5.737330750087351</v>
       </c>
       <c r="C84" t="n">
-        <v>2731679802.387777</v>
+        <v>3785343841.910222</v>
       </c>
       <c r="D84" t="n">
         <v>0.9999</v>
@@ -1620,7 +1620,7 @@
         <v>8.385313346191296</v>
       </c>
       <c r="C85" t="n">
-        <v>2169833367.797453</v>
+        <v>3335866694.237963</v>
       </c>
       <c r="D85" t="n">
         <v>0.999</v>
@@ -1634,7 +1634,7 @@
         <v>6.876305314188144</v>
       </c>
       <c r="C86" t="n">
-        <v>2603768078.525045</v>
+        <v>3683014462.820036</v>
       </c>
       <c r="D86" t="n">
         <v>0.9999</v>
@@ -1648,7 +1648,7 @@
         <v>8.682392834850489</v>
       </c>
       <c r="C87" t="n">
-        <v>641517913.4423175</v>
+        <v>2113214330.753854</v>
       </c>
       <c r="D87" t="n">
         <v>0.9</v>
@@ -1662,7 +1662,7 @@
         <v>9.531305358935807</v>
       </c>
       <c r="C88" t="n">
-        <v>2011459638.254365</v>
+        <v>3209167710.603492</v>
       </c>
       <c r="D88" t="n">
         <v>0.99</v>
@@ -1676,7 +1676,7 @@
         <v>7.618810578153383</v>
       </c>
       <c r="C89" t="n">
-        <v>2751362445.511773</v>
+        <v>3801089956.409418</v>
       </c>
       <c r="D89" t="n">
         <v>0.999</v>
@@ -1690,7 +1690,7 @@
         <v>8.860750433709352</v>
       </c>
       <c r="C90" t="n">
-        <v>795367759.4722557</v>
+        <v>2236294207.577805</v>
       </c>
       <c r="D90" t="n">
         <v>0.9</v>
@@ -1704,7 +1704,7 @@
         <v>7.192586577095136</v>
       </c>
       <c r="C91" t="n">
-        <v>1027972136.864807</v>
+        <v>2422377709.491845</v>
       </c>
       <c r="D91" t="n">
         <v>0.9</v>
@@ -1718,7 +1718,7 @@
         <v>5.212535645731624</v>
       </c>
       <c r="C92" t="n">
-        <v>1706664567.268108</v>
+        <v>2965331653.814487</v>
       </c>
       <c r="D92" t="n">
         <v>0.9999</v>
@@ -1732,7 +1732,7 @@
         <v>7.047870276338123</v>
       </c>
       <c r="C93" t="n">
-        <v>2137109018.161066</v>
+        <v>3309687214.528853</v>
       </c>
       <c r="D93" t="n">
         <v>0.9</v>
@@ -1746,7 +1746,7 @@
         <v>6.317204956216321</v>
       </c>
       <c r="C94" t="n">
-        <v>2135920435.455437</v>
+        <v>3308736348.364349</v>
       </c>
       <c r="D94" t="n">
         <v>0.999</v>
@@ -1760,7 +1760,7 @@
         <v>6.223590750203218</v>
       </c>
       <c r="C95" t="n">
-        <v>615949149.0688885</v>
+        <v>2092759319.255111</v>
       </c>
       <c r="D95" t="n">
         <v>0.9</v>
@@ -1774,7 +1774,7 @@
         <v>8.933800990309258</v>
       </c>
       <c r="C96" t="n">
-        <v>2901303361.514927</v>
+        <v>3921042689.211942</v>
       </c>
       <c r="D96" t="n">
         <v>0.99</v>
@@ -1788,7 +1788,7 @@
         <v>9.93753644259913</v>
       </c>
       <c r="C97" t="n">
-        <v>1026247160.298162</v>
+        <v>2420997728.23853</v>
       </c>
       <c r="D97" t="n">
         <v>0.99</v>
@@ -1802,7 +1802,7 @@
         <v>6.531980065306724</v>
       </c>
       <c r="C98" t="n">
-        <v>2419744668.676761</v>
+        <v>3535795734.941409</v>
       </c>
       <c r="D98" t="n">
         <v>0.99</v>
@@ -1816,7 +1816,7 @@
         <v>6.086825609080392</v>
       </c>
       <c r="C99" t="n">
-        <v>608257181.2788763</v>
+        <v>2086605745.023101</v>
       </c>
       <c r="D99" t="n">
         <v>0.9999</v>
@@ -1830,7 +1830,7 @@
         <v>8.676454889201713</v>
       </c>
       <c r="C100" t="n">
-        <v>1993468973.094893</v>
+        <v>3194775178.475915</v>
       </c>
       <c r="D100" t="n">
         <v>0.99</v>
@@ -1844,7 +1844,7 @@
         <v>9.331837192866423</v>
       </c>
       <c r="C101" t="n">
-        <v>1524648938.142527</v>
+        <v>2819719150.514021</v>
       </c>
       <c r="D101" t="n">
         <v>0.999</v>
@@ -1858,7 +1858,7 @@
         <v>8.854420884138056</v>
       </c>
       <c r="C102" t="n">
-        <v>2268090555.524024</v>
+        <v>3414472444.419219</v>
       </c>
       <c r="D102" t="n">
         <v>0.99</v>
@@ -1872,7 +1872,7 @@
         <v>7.515591010486511</v>
       </c>
       <c r="C103" t="n">
-        <v>1650788290.277534</v>
+        <v>2920630632.222028</v>
       </c>
       <c r="D103" t="n">
         <v>0.999</v>
@@ -1886,7 +1886,7 @@
         <v>5.965855373508452</v>
       </c>
       <c r="C104" t="n">
-        <v>1753378664.940421</v>
+        <v>3002702931.952337</v>
       </c>
       <c r="D104" t="n">
         <v>0.9999</v>
@@ -1900,7 +1900,7 @@
         <v>7.714583692303524</v>
       </c>
       <c r="C105" t="n">
-        <v>2574374951.822876</v>
+        <v>3659499961.458301</v>
       </c>
       <c r="D105" t="n">
         <v>0.9999</v>
@@ -1914,7 +1914,7 @@
         <v>9.759955919288128</v>
       </c>
       <c r="C106" t="n">
-        <v>2409906105.609439</v>
+        <v>3527924884.487551</v>
       </c>
       <c r="D106" t="n">
         <v>0.999</v>
@@ -1928,7 +1928,7 @@
         <v>8.765478589612465</v>
       </c>
       <c r="C107" t="n">
-        <v>1454970315.131903</v>
+        <v>2763976252.105522</v>
       </c>
       <c r="D107" t="n">
         <v>0.9</v>
@@ -1942,7 +1942,7 @@
         <v>9.700123566268346</v>
       </c>
       <c r="C108" t="n">
-        <v>2999012482.561407</v>
+        <v>3999209986.049125</v>
       </c>
       <c r="D108" t="n">
         <v>0.999</v>
@@ -1956,7 +1956,7 @@
         <v>6.455982073168022</v>
       </c>
       <c r="C109" t="n">
-        <v>2006938848.368111</v>
+        <v>3205551078.694489</v>
       </c>
       <c r="D109" t="n">
         <v>0.999</v>
@@ -1970,7 +1970,7 @@
         <v>7.949506374835217</v>
       </c>
       <c r="C110" t="n">
-        <v>1231371147.578708</v>
+        <v>2585096918.062966</v>
       </c>
       <c r="D110" t="n">
         <v>0.999</v>
@@ -1984,7 +1984,7 @@
         <v>5.36953659145887</v>
       </c>
       <c r="C111" t="n">
-        <v>992097603.3071303</v>
+        <v>2393678082.645704</v>
       </c>
       <c r="D111" t="n">
         <v>0.9</v>
@@ -1998,7 +1998,7 @@
         <v>5.182411707529574</v>
       </c>
       <c r="C112" t="n">
-        <v>1459830723.237282</v>
+        <v>2767864578.589826</v>
       </c>
       <c r="D112" t="n">
         <v>0.999</v>
@@ -2012,7 +2012,7 @@
         <v>7.248581356798459</v>
       </c>
       <c r="C113" t="n">
-        <v>2234748619.336723</v>
+        <v>3387798895.469378</v>
       </c>
       <c r="D113" t="n">
         <v>0.99</v>
@@ -2026,7 +2026,7 @@
         <v>6.284801997244228</v>
       </c>
       <c r="C114" t="n">
-        <v>531621601.4119067</v>
+        <v>2025297281.129525</v>
       </c>
       <c r="D114" t="n">
         <v>0.9</v>
@@ -2040,7 +2040,7 @@
         <v>8.67142394245983</v>
       </c>
       <c r="C115" t="n">
-        <v>1224556831.317172</v>
+        <v>2579645465.053738</v>
       </c>
       <c r="D115" t="n">
         <v>0.999</v>
@@ -2054,7 +2054,7 @@
         <v>7.517230369335895</v>
       </c>
       <c r="C116" t="n">
-        <v>505523171.5018314</v>
+        <v>2004418537.201465</v>
       </c>
       <c r="D116" t="n">
         <v>0.999</v>
@@ -2068,7 +2068,7 @@
         <v>9.771233344567799</v>
       </c>
       <c r="C117" t="n">
-        <v>2422324850.049645</v>
+        <v>3537859880.039716</v>
       </c>
       <c r="D117" t="n">
         <v>0.9999</v>
@@ -2082,7 +2082,7 @@
         <v>6.495034898705534</v>
       </c>
       <c r="C118" t="n">
-        <v>2337179265.764226</v>
+        <v>3469743412.611381</v>
       </c>
       <c r="D118" t="n">
         <v>0.99</v>
@@ -2096,7 +2096,7 @@
         <v>7.538654331550612</v>
       </c>
       <c r="C119" t="n">
-        <v>1073688469.968071</v>
+        <v>2458950775.974457</v>
       </c>
       <c r="D119" t="n">
         <v>0.999</v>
@@ -2110,7 +2110,7 @@
         <v>5.931002335795605</v>
       </c>
       <c r="C120" t="n">
-        <v>525360916.9513386</v>
+        <v>2020288733.561071</v>
       </c>
       <c r="D120" t="n">
         <v>0.99</v>
@@ -2124,7 +2124,7 @@
         <v>5.056805143634855</v>
       </c>
       <c r="C121" t="n">
-        <v>1560206235.601748</v>
+        <v>2848164988.481399</v>
       </c>
       <c r="D121" t="n">
         <v>0.99</v>
@@ -2138,7 +2138,7 @@
         <v>9.566458643242793</v>
       </c>
       <c r="C122" t="n">
-        <v>993230276.3310909</v>
+        <v>2394584221.064873</v>
       </c>
       <c r="D122" t="n">
         <v>0.9</v>
@@ -2152,7 +2152,7 @@
         <v>7.599494686069336</v>
       </c>
       <c r="C123" t="n">
-        <v>2989557781.385848</v>
+        <v>3991646225.108678</v>
       </c>
       <c r="D123" t="n">
         <v>0.99</v>
@@ -2166,7 +2166,7 @@
         <v>7.680460829010335</v>
       </c>
       <c r="C124" t="n">
-        <v>1443965768.524582</v>
+        <v>2755172614.819665</v>
       </c>
       <c r="D124" t="n">
         <v>0.9</v>
@@ -2180,7 +2180,7 @@
         <v>9.118362063116772</v>
       </c>
       <c r="C125" t="n">
-        <v>963571823.8590908</v>
+        <v>2370857459.087273</v>
       </c>
       <c r="D125" t="n">
         <v>0.99</v>
@@ -2194,7 +2194,7 @@
         <v>6.718238604788663</v>
       </c>
       <c r="C126" t="n">
-        <v>2138031763.507066</v>
+        <v>3310425410.805653</v>
       </c>
       <c r="D126" t="n">
         <v>0.99</v>
@@ -2208,7 +2208,7 @@
         <v>9.342447963803604</v>
       </c>
       <c r="C127" t="n">
-        <v>1592168889.457128</v>
+        <v>2873735111.565702</v>
       </c>
       <c r="D127" t="n">
         <v>0.99</v>
@@ -2222,7 +2222,7 @@
         <v>7.878210745685638</v>
       </c>
       <c r="C128" t="n">
-        <v>902077935.2678502</v>
+        <v>2321662348.21428</v>
       </c>
       <c r="D128" t="n">
         <v>0.9</v>
@@ -2236,7 +2236,7 @@
         <v>9.094392195284206</v>
       </c>
       <c r="C129" t="n">
-        <v>2668747394.918377</v>
+        <v>3734997915.934702</v>
       </c>
       <c r="D129" t="n">
         <v>0.9999</v>
@@ -2250,7 +2250,7 @@
         <v>8.849305886631315</v>
       </c>
       <c r="C130" t="n">
-        <v>986320763.742234</v>
+        <v>2389056610.993787</v>
       </c>
       <c r="D130" t="n">
         <v>0.9</v>
@@ -2264,7 +2264,7 @@
         <v>9.424847261070543</v>
       </c>
       <c r="C131" t="n">
-        <v>2383891755.217517</v>
+        <v>3507113404.174014</v>
       </c>
       <c r="D131" t="n">
         <v>0.9</v>
@@ -2278,7 +2278,7 @@
         <v>5.610823464646014</v>
       </c>
       <c r="C132" t="n">
-        <v>1638525192.341307</v>
+        <v>2910820153.873046</v>
       </c>
       <c r="D132" t="n">
         <v>0.9</v>
@@ -2292,7 +2292,7 @@
         <v>6.394941865800003</v>
       </c>
       <c r="C133" t="n">
-        <v>2126131795.451333</v>
+        <v>3300905436.361066</v>
       </c>
       <c r="D133" t="n">
         <v>0.999</v>
@@ -2306,7 +2306,7 @@
         <v>8.022644085371336</v>
       </c>
       <c r="C134" t="n">
-        <v>2665569530.850842</v>
+        <v>3732455624.680674</v>
       </c>
       <c r="D134" t="n">
         <v>0.999</v>
@@ -2320,7 +2320,7 @@
         <v>7.816782014339521</v>
       </c>
       <c r="C135" t="n">
-        <v>921452841.8649971</v>
+        <v>2337162273.491998</v>
       </c>
       <c r="D135" t="n">
         <v>0.9</v>
@@ -2334,7 +2334,7 @@
         <v>6.101000157680669</v>
       </c>
       <c r="C136" t="n">
-        <v>2469993238.564501</v>
+        <v>3575994590.851601</v>
       </c>
       <c r="D136" t="n">
         <v>0.999</v>
@@ -2348,7 +2348,7 @@
         <v>8.200561253705281</v>
       </c>
       <c r="C137" t="n">
-        <v>1286483462.202189</v>
+        <v>2629186769.761752</v>
       </c>
       <c r="D137" t="n">
         <v>0.99</v>
@@ -2362,7 +2362,7 @@
         <v>5.54732768961261</v>
       </c>
       <c r="C138" t="n">
-        <v>1594223370.593113</v>
+        <v>2875378696.474491</v>
       </c>
       <c r="D138" t="n">
         <v>0.9999</v>
@@ -2376,7 +2376,7 @@
         <v>9.191035277135235</v>
       </c>
       <c r="C139" t="n">
-        <v>2961581710.887008</v>
+        <v>3969265368.709606</v>
       </c>
       <c r="D139" t="n">
         <v>0.999</v>
@@ -2390,7 +2390,7 @@
         <v>9.87944987340385</v>
       </c>
       <c r="C140" t="n">
-        <v>1975904942.844907</v>
+        <v>3180723954.275926</v>
       </c>
       <c r="D140" t="n">
         <v>0.9999</v>
@@ -2404,7 +2404,7 @@
         <v>8.489362524352748</v>
       </c>
       <c r="C141" t="n">
-        <v>927039476.6136951</v>
+        <v>2341631581.290956</v>
       </c>
       <c r="D141" t="n">
         <v>0.9999</v>
@@ -2418,7 +2418,7 @@
         <v>8.937093513897301</v>
       </c>
       <c r="C142" t="n">
-        <v>940773743.7509789</v>
+        <v>2352618995.000783</v>
       </c>
       <c r="D142" t="n">
         <v>0.9</v>
@@ -2432,7 +2432,7 @@
         <v>8.334191465650084</v>
       </c>
       <c r="C143" t="n">
-        <v>2373004385.32259</v>
+        <v>3498403508.258072</v>
       </c>
       <c r="D143" t="n">
         <v>0.9999</v>
@@ -2446,7 +2446,7 @@
         <v>9.542506241693111</v>
       </c>
       <c r="C144" t="n">
-        <v>1488923806.043794</v>
+        <v>2791139044.835035</v>
       </c>
       <c r="D144" t="n">
         <v>0.999</v>
@@ -2460,7 +2460,7 @@
         <v>5.573220273729865</v>
       </c>
       <c r="C145" t="n">
-        <v>2706089191.132353</v>
+        <v>3764871352.905883</v>
       </c>
       <c r="D145" t="n">
         <v>0.9</v>
@@ -2474,7 +2474,7 @@
         <v>7.263238582829572</v>
       </c>
       <c r="C146" t="n">
-        <v>1622796821.449897</v>
+        <v>2898237457.159917</v>
       </c>
       <c r="D146" t="n">
         <v>0.9</v>
@@ -2488,7 +2488,7 @@
         <v>7.721886767168597</v>
       </c>
       <c r="C147" t="n">
-        <v>899628337.3875953</v>
+        <v>2319702669.910076</v>
       </c>
       <c r="D147" t="n">
         <v>0.999</v>
@@ -2502,7 +2502,7 @@
         <v>7.348722096049807</v>
       </c>
       <c r="C148" t="n">
-        <v>2088999715.474046</v>
+        <v>3271199772.379237</v>
       </c>
       <c r="D148" t="n">
         <v>0.9</v>
@@ -2516,7 +2516,7 @@
         <v>5.235935790873921</v>
       </c>
       <c r="C149" t="n">
-        <v>2066620631.091411</v>
+        <v>3253296504.873129</v>
       </c>
       <c r="D149" t="n">
         <v>0.9</v>
@@ -2530,7 +2530,7 @@
         <v>7.383215609083218</v>
       </c>
       <c r="C150" t="n">
-        <v>1871228684.336631</v>
+        <v>3096982947.469305</v>
       </c>
       <c r="D150" t="n">
         <v>0.999</v>
@@ -2544,7 +2544,7 @@
         <v>9.561975709941713</v>
       </c>
       <c r="C151" t="n">
-        <v>1702560454.634873</v>
+        <v>2962048363.707899</v>
       </c>
       <c r="D151" t="n">
         <v>0.999</v>
@@ -2558,7 +2558,7 @@
         <v>8.783684066274695</v>
       </c>
       <c r="C152" t="n">
-        <v>804913602.6028707</v>
+        <v>2243930882.082296</v>
       </c>
       <c r="D152" t="n">
         <v>0.9999</v>
@@ -2572,7 +2572,7 @@
         <v>7.113858320287951</v>
       </c>
       <c r="C153" t="n">
-        <v>1042201799.686504</v>
+        <v>2433761439.749203</v>
       </c>
       <c r="D153" t="n">
         <v>0.999</v>
@@ -2586,7 +2586,7 @@
         <v>5.51165984730045</v>
       </c>
       <c r="C154" t="n">
-        <v>2545725222.778549</v>
+        <v>3636580178.222839</v>
       </c>
       <c r="D154" t="n">
         <v>0.9999</v>
@@ -2600,7 +2600,7 @@
         <v>8.349484920008285</v>
       </c>
       <c r="C155" t="n">
-        <v>2851382000.309461</v>
+        <v>3881105600.247569</v>
       </c>
       <c r="D155" t="n">
         <v>0.9999</v>
@@ -2614,7 +2614,7 @@
         <v>8.476261094694122</v>
       </c>
       <c r="C156" t="n">
-        <v>2923952190.927437</v>
+        <v>3939161752.74195</v>
       </c>
       <c r="D156" t="n">
         <v>0.99</v>
@@ -2628,7 +2628,7 @@
         <v>6.743179714687894</v>
       </c>
       <c r="C157" t="n">
-        <v>1219599758.485664</v>
+        <v>2575679806.788531</v>
       </c>
       <c r="D157" t="n">
         <v>0.9</v>
@@ -2642,7 +2642,7 @@
         <v>7.809160726455841</v>
       </c>
       <c r="C158" t="n">
-        <v>1510619308.489529</v>
+        <v>2808495446.791623</v>
       </c>
       <c r="D158" t="n">
         <v>0.9999</v>
@@ -2656,7 +2656,7 @@
         <v>7.294137297724353</v>
       </c>
       <c r="C159" t="n">
-        <v>2347598081.608984</v>
+        <v>3478078465.287188</v>
       </c>
       <c r="D159" t="n">
         <v>0.9</v>
@@ -2670,7 +2670,7 @@
         <v>7.713426330930996</v>
       </c>
       <c r="C160" t="n">
-        <v>2334720139.06502</v>
+        <v>3467776111.252016</v>
       </c>
       <c r="D160" t="n">
         <v>0.9999</v>
@@ -2684,7 +2684,7 @@
         <v>9.370121538389078</v>
       </c>
       <c r="C161" t="n">
-        <v>2886088419.608402</v>
+        <v>3908870735.686722</v>
       </c>
       <c r="D161" t="n">
         <v>0.999</v>
@@ -2698,7 +2698,7 @@
         <v>5.867575711269144</v>
       </c>
       <c r="C162" t="n">
-        <v>1611075280.076413</v>
+        <v>2888860224.061131</v>
       </c>
       <c r="D162" t="n">
         <v>0.9999</v>
@@ -2712,7 +2712,7 @@
         <v>7.598874770936579</v>
       </c>
       <c r="C163" t="n">
-        <v>1979803753.940564</v>
+        <v>3183843003.152452</v>
       </c>
       <c r="D163" t="n">
         <v>0.9999</v>
@@ -2726,7 +2726,7 @@
         <v>6.084571537553613</v>
       </c>
       <c r="C164" t="n">
-        <v>707879036.93288</v>
+        <v>2166303229.546304</v>
       </c>
       <c r="D164" t="n">
         <v>0.99</v>
@@ -2740,7 +2740,7 @@
         <v>8.636257614984107</v>
       </c>
       <c r="C165" t="n">
-        <v>2039962581.595063</v>
+        <v>3231970065.276051</v>
       </c>
       <c r="D165" t="n">
         <v>0.9999</v>
@@ -2754,7 +2754,7 @@
         <v>6.146573381762737</v>
       </c>
       <c r="C166" t="n">
-        <v>2321098074.814573</v>
+        <v>3456878459.851658</v>
       </c>
       <c r="D166" t="n">
         <v>0.9999</v>
@@ -2768,7 +2768,7 @@
         <v>8.327371668757642</v>
       </c>
       <c r="C167" t="n">
-        <v>2199732416.766175</v>
+        <v>3359785933.41294</v>
       </c>
       <c r="D167" t="n">
         <v>0.9</v>
@@ -2782,7 +2782,7 @@
         <v>8.624311950442753</v>
       </c>
       <c r="C168" t="n">
-        <v>875629030.9208113</v>
+        <v>2300503224.736649</v>
       </c>
       <c r="D168" t="n">
         <v>0.99</v>
@@ -2796,7 +2796,7 @@
         <v>5.48244713295558</v>
       </c>
       <c r="C169" t="n">
-        <v>2889275891.119272</v>
+        <v>3911420712.895418</v>
       </c>
       <c r="D169" t="n">
         <v>0.9</v>
@@ -2810,7 +2810,7 @@
         <v>7.873149543398464</v>
       </c>
       <c r="C170" t="n">
-        <v>2664406360.514993</v>
+        <v>3731525088.411994</v>
       </c>
       <c r="D170" t="n">
         <v>0.9</v>
@@ -2824,7 +2824,7 @@
         <v>7.877127904465733</v>
       </c>
       <c r="C171" t="n">
-        <v>1932049436.312489</v>
+        <v>3145639549.049992</v>
       </c>
       <c r="D171" t="n">
         <v>0.9</v>
@@ -2838,7 +2838,7 @@
         <v>6.962844980444306</v>
       </c>
       <c r="C172" t="n">
-        <v>2923446808.247869</v>
+        <v>3938757446.598295</v>
       </c>
       <c r="D172" t="n">
         <v>0.9999</v>
@@ -2852,7 +2852,7 @@
         <v>6.56182312852469</v>
       </c>
       <c r="C173" t="n">
-        <v>1152806247.166273</v>
+        <v>2522244997.733018</v>
       </c>
       <c r="D173" t="n">
         <v>0.9</v>
@@ -2866,7 +2866,7 @@
         <v>9.10708816182705</v>
       </c>
       <c r="C174" t="n">
-        <v>1087253566.3403</v>
+        <v>2469802853.07224</v>
       </c>
       <c r="D174" t="n">
         <v>0.9999</v>
@@ -2880,7 +2880,7 @@
         <v>9.964183993301885</v>
       </c>
       <c r="C175" t="n">
-        <v>1372787903.131142</v>
+        <v>2698230322.504913</v>
       </c>
       <c r="D175" t="n">
         <v>0.9999</v>
@@ -2894,7 +2894,7 @@
         <v>9.321762102442536</v>
       </c>
       <c r="C176" t="n">
-        <v>2902840474.547933</v>
+        <v>3922272379.638346</v>
       </c>
       <c r="D176" t="n">
         <v>0.9</v>
@@ -2908,7 +2908,7 @@
         <v>6.445367827304329</v>
       </c>
       <c r="C177" t="n">
-        <v>2905318353.200593</v>
+        <v>3924254682.560475</v>
       </c>
       <c r="D177" t="n">
         <v>0.9</v>
@@ -2922,7 +2922,7 @@
         <v>8.116432027048425</v>
       </c>
       <c r="C178" t="n">
-        <v>1927374119.733077</v>
+        <v>3141899295.786462</v>
       </c>
       <c r="D178" t="n">
         <v>0.99</v>
@@ -2936,7 +2936,7 @@
         <v>6.403195056018463</v>
       </c>
       <c r="C179" t="n">
-        <v>2239456362.757734</v>
+        <v>3391565090.206187</v>
       </c>
       <c r="D179" t="n">
         <v>0.999</v>
@@ -2950,7 +2950,7 @@
         <v>9.666230365836086</v>
       </c>
       <c r="C180" t="n">
-        <v>2448388219.343205</v>
+        <v>3558710575.474564</v>
       </c>
       <c r="D180" t="n">
         <v>0.9999</v>
@@ -2964,7 +2964,7 @@
         <v>7.471240580425153</v>
       </c>
       <c r="C181" t="n">
-        <v>1036867974.858187</v>
+        <v>2429494379.886549</v>
       </c>
       <c r="D181" t="n">
         <v>0.999</v>
@@ -2978,7 +2978,7 @@
         <v>5.992338955038253</v>
       </c>
       <c r="C182" t="n">
-        <v>2140059511.298772</v>
+        <v>3312047609.039018</v>
       </c>
       <c r="D182" t="n">
         <v>0.99</v>
@@ -2992,7 +2992,7 @@
         <v>7.634058046714678</v>
       </c>
       <c r="C183" t="n">
-        <v>1839202788.430913</v>
+        <v>3071362230.74473</v>
       </c>
       <c r="D183" t="n">
         <v>0.99</v>
@@ -3006,7 +3006,7 @@
         <v>9.932042753272246</v>
       </c>
       <c r="C184" t="n">
-        <v>710563535.5899063</v>
+        <v>2168450828.471925</v>
       </c>
       <c r="D184" t="n">
         <v>0.999</v>
@@ -3020,7 +3020,7 @@
         <v>5.251444232958472</v>
       </c>
       <c r="C185" t="n">
-        <v>1189712571.209549</v>
+        <v>2551770056.967639</v>
       </c>
       <c r="D185" t="n">
         <v>0.9999</v>
@@ -3034,7 +3034,7 @@
         <v>7.240184665724438</v>
       </c>
       <c r="C186" t="n">
-        <v>1902011667.400329</v>
+        <v>3121609333.920263</v>
       </c>
       <c r="D186" t="n">
         <v>0.999</v>
@@ -3048,7 +3048,7 @@
         <v>9.444763752969507</v>
       </c>
       <c r="C187" t="n">
-        <v>559656906.8869915</v>
+        <v>2047725525.509593</v>
       </c>
       <c r="D187" t="n">
         <v>0.999</v>
@@ -3062,7 +3062,7 @@
         <v>6.739893668201628</v>
       </c>
       <c r="C188" t="n">
-        <v>618522443.6276197</v>
+        <v>2094817954.902096</v>
       </c>
       <c r="D188" t="n">
         <v>0.999</v>
@@ -3076,7 +3076,7 @@
         <v>5.92076049786708</v>
       </c>
       <c r="C189" t="n">
-        <v>1443746263.512936</v>
+        <v>2754997010.810349</v>
       </c>
       <c r="D189" t="n">
         <v>0.9</v>
@@ -3090,7 +3090,7 @@
         <v>5.387781606894188</v>
       </c>
       <c r="C190" t="n">
-        <v>850939019.7085552</v>
+        <v>2280751215.766844</v>
       </c>
       <c r="D190" t="n">
         <v>0.99</v>
@@ -3104,7 +3104,7 @@
         <v>5.523056908103191</v>
       </c>
       <c r="C191" t="n">
-        <v>513692451.0549755</v>
+        <v>2010953960.84398</v>
       </c>
       <c r="D191" t="n">
         <v>0.99</v>
@@ -3118,7 +3118,7 @@
         <v>9.760427587612066</v>
       </c>
       <c r="C192" t="n">
-        <v>2698354749.956564</v>
+        <v>3758683799.965251</v>
       </c>
       <c r="D192" t="n">
         <v>0.9</v>
@@ -3132,7 +3132,7 @@
         <v>7.419183241991977</v>
       </c>
       <c r="C193" t="n">
-        <v>2868663309.424706</v>
+        <v>3894930647.539765</v>
       </c>
       <c r="D193" t="n">
         <v>0.99</v>
@@ -3146,7 +3146,7 @@
         <v>9.985242780869459</v>
       </c>
       <c r="C194" t="n">
-        <v>744967924.0122105</v>
+        <v>2195974339.209768</v>
       </c>
       <c r="D194" t="n">
         <v>0.99</v>
@@ -3160,7 +3160,7 @@
         <v>7.481667129286762</v>
       </c>
       <c r="C195" t="n">
-        <v>820054404.542156</v>
+        <v>2256043523.633725</v>
       </c>
       <c r="D195" t="n">
         <v>0.99</v>
@@ -3174,7 +3174,7 @@
         <v>7.378575173006013</v>
       </c>
       <c r="C196" t="n">
-        <v>2496768324.851472</v>
+        <v>3597414659.881177</v>
       </c>
       <c r="D196" t="n">
         <v>0.999</v>
@@ -3188,7 +3188,7 @@
         <v>8.84497705949499</v>
       </c>
       <c r="C197" t="n">
-        <v>1326022295.084183</v>
+        <v>2660817836.067347</v>
       </c>
       <c r="D197" t="n">
         <v>0.999</v>
@@ -3202,7 +3202,7 @@
         <v>5.674606221140627</v>
       </c>
       <c r="C198" t="n">
-        <v>2595411787.962806</v>
+        <v>3676329430.370245</v>
       </c>
       <c r="D198" t="n">
         <v>0.9</v>
@@ -3216,7 +3216,7 @@
         <v>9.712678791110495</v>
       </c>
       <c r="C199" t="n">
-        <v>2556584242.951637</v>
+        <v>3645267394.36131</v>
       </c>
       <c r="D199" t="n">
         <v>0.999</v>
@@ -3230,7 +3230,7 @@
         <v>9.982895955534421</v>
       </c>
       <c r="C200" t="n">
-        <v>1779781435.086656</v>
+        <v>3023825148.069324</v>
       </c>
       <c r="D200" t="n">
         <v>0.99</v>
@@ -3244,7 +3244,7 @@
         <v>9.974578610043086</v>
       </c>
       <c r="C201" t="n">
-        <v>2385496719.770485</v>
+        <v>3508397375.816388</v>
       </c>
       <c r="D201" t="n">
         <v>0.999</v>

--- a/data/task_parameters_evaluation.xlsx
+++ b/data/task_parameters_evaluation.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +452,11 @@
           <t>Reliability_Requirement</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Deadline</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -461,7 +469,10 @@
         <v>2041275211.227155</v>
       </c>
       <c r="D2" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.212818468495464</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +486,10 @@
         <v>2688338482.293077</v>
       </c>
       <c r="D3" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1.556040607894298</v>
       </c>
     </row>
     <row r="4">
@@ -491,6 +505,9 @@
       <c r="D4" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>1.581902519760415</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -503,7 +520,10 @@
         <v>3735694164.185751</v>
       </c>
       <c r="D5" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2.020003575964683</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +537,10 @@
         <v>2240558336.643902</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1.3889085233927</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +554,10 @@
         <v>3203987703.924151</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1.857058741238089</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +571,10 @@
         <v>3433930626.273855</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.778083549458344</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +588,10 @@
         <v>3370273429.331845</v>
       </c>
       <c r="D9" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1.814198535508302</v>
       </c>
     </row>
     <row r="10">
@@ -575,6 +607,9 @@
       <c r="D10" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>1.677637753059141</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -587,7 +622,10 @@
         <v>2759023509.556121</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1.552543171661607</v>
       </c>
     </row>
     <row r="12">
@@ -603,6 +641,9 @@
       <c r="D12" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>2.142141429443261</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -617,6 +658,9 @@
       <c r="D13" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>1.74497396567694</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -629,7 +673,10 @@
         <v>3000400843.832637</v>
       </c>
       <c r="D14" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1.523024796870295</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +690,10 @@
         <v>3280787914.51978</v>
       </c>
       <c r="D15" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1.703367970046409</v>
       </c>
     </row>
     <row r="16">
@@ -659,6 +709,9 @@
       <c r="D16" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E16" s="2" t="n">
+        <v>1.845324083172495</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -671,7 +724,10 @@
         <v>3106420976.775494</v>
       </c>
       <c r="D17" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1.911171943376699</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +741,10 @@
         <v>2076104034.388592</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1.484036220510622</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +758,10 @@
         <v>3473797094.482754</v>
       </c>
       <c r="D19" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2.024449391788053</v>
       </c>
     </row>
     <row r="20">
@@ -715,6 +777,9 @@
       <c r="D20" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>1.188196996624074</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -727,7 +792,10 @@
         <v>2757864503.07458</v>
       </c>
       <c r="D21" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1.470958654046553</v>
       </c>
     </row>
     <row r="22">
@@ -743,6 +811,9 @@
       <c r="D22" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>1.406331118881766</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -755,7 +826,10 @@
         <v>2032945606.508714</v>
       </c>
       <c r="D23" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1.330283753959856</v>
       </c>
     </row>
     <row r="24">
@@ -771,6 +845,9 @@
       <c r="D24" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E24" s="2" t="n">
+        <v>1.383720009286006</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -783,7 +860,10 @@
         <v>2817754637.235204</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1.518042671911211</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +877,10 @@
         <v>2416009056.58981</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1.526567894361387</v>
       </c>
     </row>
     <row r="27">
@@ -813,6 +896,9 @@
       <c r="D27" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>2.154279518994858</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -825,7 +911,10 @@
         <v>3608988843.308181</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1.87244462235959</v>
       </c>
     </row>
     <row r="29">
@@ -839,7 +928,10 @@
         <v>3938892596.769102</v>
       </c>
       <c r="D29" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2.079511806202829</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +945,10 @@
         <v>3969598583.566524</v>
       </c>
       <c r="D30" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1.936141847610436</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +962,10 @@
         <v>3740078425.248031</v>
       </c>
       <c r="D31" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2.147916935132584</v>
       </c>
     </row>
     <row r="32">
@@ -883,6 +981,9 @@
       <c r="D32" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E32" s="2" t="n">
+        <v>1.909512901283922</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -897,6 +998,9 @@
       <c r="D33" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>1.945823310769555</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -909,7 +1013,10 @@
         <v>3587128529.70233</v>
       </c>
       <c r="D34" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>1.83450603823928</v>
       </c>
     </row>
     <row r="35">
@@ -925,6 +1032,9 @@
       <c r="D35" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E35" s="2" t="n">
+        <v>1.584704213344871</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -937,7 +1047,10 @@
         <v>3067418057.144017</v>
       </c>
       <c r="D36" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1.860280097895857</v>
       </c>
     </row>
     <row r="37">
@@ -951,7 +1064,10 @@
         <v>3949892874.754253</v>
       </c>
       <c r="D37" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>2.026353702313143</v>
       </c>
     </row>
     <row r="38">
@@ -967,6 +1083,9 @@
       <c r="D38" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E38" s="2" t="n">
+        <v>1.448770803160961</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -979,7 +1098,10 @@
         <v>3170684455.030489</v>
       </c>
       <c r="D39" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1.806131273437314</v>
       </c>
     </row>
     <row r="40">
@@ -993,7 +1115,10 @@
         <v>2700858981.362084</v>
       </c>
       <c r="D40" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1.549355855614231</v>
       </c>
     </row>
     <row r="41">
@@ -1007,7 +1132,10 @@
         <v>3115899732.946083</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1.568958916152183</v>
       </c>
     </row>
     <row r="42">
@@ -1023,6 +1151,9 @@
       <c r="D42" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E42" s="2" t="n">
+        <v>1.270183485127232</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1035,7 +1166,10 @@
         <v>2623989209.005305</v>
       </c>
       <c r="D43" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1.57511585062024</v>
       </c>
     </row>
     <row r="44">
@@ -1051,6 +1185,9 @@
       <c r="D44" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E44" s="2" t="n">
+        <v>1.582693498674804</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1065,6 +1202,9 @@
       <c r="D45" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E45" s="2" t="n">
+        <v>1.937277814021893</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1077,7 +1217,10 @@
         <v>3193189099.733428</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1.974975651400131</v>
       </c>
     </row>
     <row r="47">
@@ -1091,7 +1234,10 @@
         <v>3866736406.083718</v>
       </c>
       <c r="D47" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>2.037225112071324</v>
       </c>
     </row>
     <row r="48">
@@ -1105,7 +1251,10 @@
         <v>3960544225.592988</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>2.261207027743499</v>
       </c>
     </row>
     <row r="49">
@@ -1119,7 +1268,10 @@
         <v>2941202865.237553</v>
       </c>
       <c r="D49" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1.878438055573497</v>
       </c>
     </row>
     <row r="50">
@@ -1135,6 +1287,9 @@
       <c r="D50" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E50" s="2" t="n">
+        <v>1.621351207586382</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1147,7 +1302,10 @@
         <v>2973286231.659394</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1.571609643279948</v>
       </c>
     </row>
     <row r="52">
@@ -1161,7 +1319,10 @@
         <v>3902970550.117238</v>
       </c>
       <c r="D52" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>2.118029290699034</v>
       </c>
     </row>
     <row r="53">
@@ -1175,7 +1336,10 @@
         <v>2345241625.663661</v>
       </c>
       <c r="D53" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1.620763506977272</v>
       </c>
     </row>
     <row r="54">
@@ -1189,7 +1353,10 @@
         <v>2372747480.491072</v>
       </c>
       <c r="D54" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1.332957747299456</v>
       </c>
     </row>
     <row r="55">
@@ -1203,7 +1370,10 @@
         <v>2836101423.651895</v>
       </c>
       <c r="D55" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1.519200146070793</v>
       </c>
     </row>
     <row r="56">
@@ -1217,7 +1387,10 @@
         <v>3861152071.530159</v>
       </c>
       <c r="D56" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>2.149701289180223</v>
       </c>
     </row>
     <row r="57">
@@ -1231,7 +1404,10 @@
         <v>2418772594.572377</v>
       </c>
       <c r="D57" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1.317055447285859</v>
       </c>
     </row>
     <row r="58">
@@ -1245,7 +1421,10 @@
         <v>2088500895.548698</v>
       </c>
       <c r="D58" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1.352411007429789</v>
       </c>
     </row>
     <row r="59">
@@ -1259,7 +1438,10 @@
         <v>2253246986.167578</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1.530224615442938</v>
       </c>
     </row>
     <row r="60">
@@ -1275,6 +1457,9 @@
       <c r="D60" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E60" s="2" t="n">
+        <v>1.5293948556016</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1289,6 +1474,9 @@
       <c r="D61" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E61" s="2" t="n">
+        <v>1.670686654795542</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1303,6 +1491,9 @@
       <c r="D62" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E62" s="2" t="n">
+        <v>2.171348224648237</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1317,6 +1508,9 @@
       <c r="D63" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E63" s="2" t="n">
+        <v>1.581790510780676</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1331,6 +1525,9 @@
       <c r="D64" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E64" s="2" t="n">
+        <v>1.787608237776563</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1343,7 +1540,10 @@
         <v>2730221501.577714</v>
       </c>
       <c r="D65" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>1.731120982301094</v>
       </c>
     </row>
     <row r="66">
@@ -1357,7 +1557,10 @@
         <v>3855127516.843309</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>1.881801092419889</v>
       </c>
     </row>
     <row r="67">
@@ -1371,7 +1574,10 @@
         <v>2602167972.519974</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>1.51259494316833</v>
       </c>
     </row>
     <row r="68">
@@ -1385,7 +1591,10 @@
         <v>3928084983.064842</v>
       </c>
       <c r="D68" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1.951237489003298</v>
       </c>
     </row>
     <row r="69">
@@ -1399,7 +1608,10 @@
         <v>2533516845.2327</v>
       </c>
       <c r="D69" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>1.711118367442579</v>
       </c>
     </row>
     <row r="70">
@@ -1413,7 +1625,10 @@
         <v>3774709127.327841</v>
       </c>
       <c r="D70" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>2.194039940752524</v>
       </c>
     </row>
     <row r="71">
@@ -1427,7 +1642,10 @@
         <v>2359585041.053266</v>
       </c>
       <c r="D71" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>1.518082285689832</v>
       </c>
     </row>
     <row r="72">
@@ -1441,7 +1659,10 @@
         <v>3899067911.866893</v>
       </c>
       <c r="D72" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>1.891711877272785</v>
       </c>
     </row>
     <row r="73">
@@ -1455,7 +1676,10 @@
         <v>2127937253.108463</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>1.198759580245301</v>
       </c>
     </row>
     <row r="74">
@@ -1469,7 +1693,10 @@
         <v>3482278841.347547</v>
       </c>
       <c r="D74" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>1.864318714983076</v>
       </c>
     </row>
     <row r="75">
@@ -1483,7 +1710,10 @@
         <v>2892749333.815838</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>1.78481992769248</v>
       </c>
     </row>
     <row r="76">
@@ -1497,7 +1727,10 @@
         <v>2346973041.075265</v>
       </c>
       <c r="D76" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>1.336339071752652</v>
       </c>
     </row>
     <row r="77">
@@ -1513,6 +1746,9 @@
       <c r="D77" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E77" s="2" t="n">
+        <v>1.496048768838295</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1525,7 +1761,10 @@
         <v>3161460799.323009</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>1.90701859980021</v>
       </c>
     </row>
     <row r="79">
@@ -1539,7 +1778,10 @@
         <v>3283967896.512748</v>
       </c>
       <c r="D79" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>1.635274937037922</v>
       </c>
     </row>
     <row r="80">
@@ -1555,6 +1797,9 @@
       <c r="D80" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E80" s="2" t="n">
+        <v>1.775062440186025</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1567,7 +1812,10 @@
         <v>2485695439.738623</v>
       </c>
       <c r="D81" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>1.511345079524683</v>
       </c>
     </row>
     <row r="82">
@@ -1581,7 +1829,10 @@
         <v>3852423964.901986</v>
       </c>
       <c r="D82" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>1.878410991935139</v>
       </c>
     </row>
     <row r="83">
@@ -1595,7 +1846,10 @@
         <v>3235750182.18655</v>
       </c>
       <c r="D83" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>1.807078246696167</v>
       </c>
     </row>
     <row r="84">
@@ -1611,6 +1865,9 @@
       <c r="D84" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E84" s="2" t="n">
+        <v>1.87374803794528</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1623,7 +1880,10 @@
         <v>3335866694.237963</v>
       </c>
       <c r="D85" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>1.913524027325861</v>
       </c>
     </row>
     <row r="86">
@@ -1639,6 +1899,9 @@
       <c r="D86" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E86" s="2" t="n">
+        <v>1.925037981618419</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1651,7 +1914,10 @@
         <v>2113214330.753854</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>1.477697710489932</v>
       </c>
     </row>
     <row r="88">
@@ -1665,7 +1931,10 @@
         <v>3209167710.603492</v>
       </c>
       <c r="D88" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>1.956213538714339</v>
       </c>
     </row>
     <row r="89">
@@ -1679,7 +1948,10 @@
         <v>3801089956.409418</v>
       </c>
       <c r="D89" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>2.027879549789762</v>
       </c>
     </row>
     <row r="90">
@@ -1693,7 +1965,10 @@
         <v>2236294207.577805</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>1.537977092742239</v>
       </c>
     </row>
     <row r="91">
@@ -1707,7 +1982,10 @@
         <v>2422377709.491845</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>1.476457350910983</v>
       </c>
     </row>
     <row r="92">
@@ -1723,6 +2001,9 @@
       <c r="D92" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E92" s="2" t="n">
+        <v>1.524408955573105</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1735,7 +2016,10 @@
         <v>3309687214.528853</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>1.798331294789814</v>
       </c>
     </row>
     <row r="94">
@@ -1749,7 +2033,10 @@
         <v>3308736348.364349</v>
       </c>
       <c r="D94" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>1.740414557523897</v>
       </c>
     </row>
     <row r="95">
@@ -1763,7 +2050,10 @@
         <v>2092759319.255111</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>1.276317841636087</v>
       </c>
     </row>
     <row r="96">
@@ -1777,7 +2067,10 @@
         <v>3921042689.211942</v>
       </c>
       <c r="D96" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>2.176524849057599</v>
       </c>
     </row>
     <row r="97">
@@ -1791,7 +2084,10 @@
         <v>2420997728.23853</v>
       </c>
       <c r="D97" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>1.692177828360484</v>
       </c>
     </row>
     <row r="98">
@@ -1805,7 +2101,10 @@
         <v>3535795734.941409</v>
       </c>
       <c r="D98" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>1.842617598487261</v>
       </c>
     </row>
     <row r="99">
@@ -1821,6 +2120,9 @@
       <c r="D99" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E99" s="2" t="n">
+        <v>1.263232611833031</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1833,7 +2135,10 @@
         <v>3194775178.475915</v>
       </c>
       <c r="D100" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>1.883465171249894</v>
       </c>
     </row>
     <row r="101">
@@ -1847,7 +2152,10 @@
         <v>2819719150.514021</v>
       </c>
       <c r="D101" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1.794222811495974</v>
       </c>
     </row>
     <row r="102">
@@ -1861,7 +2169,10 @@
         <v>3414472444.419219</v>
       </c>
       <c r="D102" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>1.980003283003237</v>
       </c>
     </row>
     <row r="103">
@@ -1875,7 +2186,10 @@
         <v>2920630632.222028</v>
       </c>
       <c r="D103" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>1.68904690660422</v>
       </c>
     </row>
     <row r="104">
@@ -1891,6 +2205,9 @@
       <c r="D104" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E104" s="2" t="n">
+        <v>1.597789877880188</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1905,6 +2222,9 @@
       <c r="D105" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E105" s="2" t="n">
+        <v>1.982242934007345</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1917,7 +2237,10 @@
         <v>3527924884.487551</v>
       </c>
       <c r="D106" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>2.093951417485858</v>
       </c>
     </row>
     <row r="107">
@@ -1931,7 +2254,10 @@
         <v>2763976252.105522</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>1.728669720587418</v>
       </c>
     </row>
     <row r="108">
@@ -1945,7 +2271,10 @@
         <v>3999209986.049125</v>
       </c>
       <c r="D108" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>2.266253117762357</v>
       </c>
     </row>
     <row r="109">
@@ -1959,7 +2288,10 @@
         <v>3205551078.694489</v>
       </c>
       <c r="D109" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>1.712590515856099</v>
       </c>
     </row>
     <row r="110">
@@ -1973,7 +2305,10 @@
         <v>2585096918.062966</v>
       </c>
       <c r="D110" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>1.597202671985138</v>
       </c>
     </row>
     <row r="111">
@@ -1987,7 +2322,10 @@
         <v>2393678082.645704</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>1.322063413326119</v>
       </c>
     </row>
     <row r="112">
@@ -2001,7 +2339,10 @@
         <v>2767864578.589826</v>
       </c>
       <c r="D112" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>1.447867071050409</v>
       </c>
     </row>
     <row r="113">
@@ -2015,7 +2356,10 @@
         <v>3387798895.469378</v>
       </c>
       <c r="D113" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>1.84348152121362</v>
       </c>
     </row>
     <row r="114">
@@ -2029,7 +2373,10 @@
         <v>2025297281.129525</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>1.25580107483449</v>
       </c>
     </row>
     <row r="115">
@@ -2043,7 +2390,10 @@
         <v>2579645465.053738</v>
       </c>
       <c r="D115" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>1.652025571041224</v>
       </c>
     </row>
     <row r="116">
@@ -2057,7 +2407,10 @@
         <v>2004418537.201465</v>
       </c>
       <c r="D116" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>1.345045957536667</v>
       </c>
     </row>
     <row r="117">
@@ -2073,6 +2426,9 @@
       <c r="D117" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E117" s="2" t="n">
+        <v>2.098571412069211</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2085,7 +2441,10 @@
         <v>3469743412.611381</v>
       </c>
       <c r="D118" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>1.814897858562204</v>
       </c>
     </row>
     <row r="119">
@@ -2099,7 +2458,10 @@
         <v>2458950775.974457</v>
       </c>
       <c r="D119" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>1.517456392689918</v>
       </c>
     </row>
     <row r="120">
@@ -2113,7 +2475,10 @@
         <v>2020288733.561071</v>
       </c>
       <c r="D120" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>1.226048598839274</v>
       </c>
     </row>
     <row r="121">
@@ -2127,7 +2492,10 @@
         <v>2848164988.481399</v>
       </c>
       <c r="D121" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>1.468133074759068</v>
       </c>
     </row>
     <row r="122">
@@ -2141,7 +2509,10 @@
         <v>2394584221.064873</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>1.653024511009065</v>
       </c>
     </row>
     <row r="123">
@@ -2155,7 +2526,10 @@
         <v>3991646225.108678</v>
       </c>
       <c r="D123" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>2.09793100969888</v>
       </c>
     </row>
     <row r="124">
@@ -2169,7 +2543,10 @@
         <v>2755172614.819665</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>1.639888668133153</v>
       </c>
     </row>
     <row r="125">
@@ -2183,7 +2560,10 @@
         <v>2370857459.087273</v>
       </c>
       <c r="D125" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>1.608813032346043</v>
       </c>
     </row>
     <row r="126">
@@ -2197,7 +2577,10 @@
         <v>3310425410.805653</v>
       </c>
       <c r="D126" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>1.772641181707996</v>
       </c>
     </row>
     <row r="127">
@@ -2211,7 +2594,10 @@
         <v>2873735111.565702</v>
       </c>
       <c r="D127" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>1.815347139647328</v>
       </c>
     </row>
     <row r="128">
@@ -2225,7 +2611,10 @@
         <v>2321662348.21428</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>1.492639956170614</v>
       </c>
     </row>
     <row r="129">
@@ -2241,6 +2630,9 @@
       <c r="D129" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E129" s="2" t="n">
+        <v>2.119297150274099</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2253,7 +2645,10 @@
         <v>2389056610.993787</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>1.59445322323147</v>
       </c>
     </row>
     <row r="131">
@@ -2267,7 +2662,10 @@
         <v>3507113404.174014</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>2.059735766010075</v>
       </c>
     </row>
     <row r="132">
@@ -2281,7 +2679,10 @@
         <v>2910820153.873046</v>
       </c>
       <c r="D132" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>1.535310289514231</v>
       </c>
     </row>
     <row r="133">
@@ -2295,7 +2696,10 @@
         <v>3300905436.361066</v>
       </c>
       <c r="D133" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>1.743597137126515</v>
       </c>
     </row>
     <row r="134">
@@ -2309,7 +2713,10 @@
         <v>3732455624.680674</v>
       </c>
       <c r="D134" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>2.03391320777283</v>
       </c>
     </row>
     <row r="135">
@@ -2323,7 +2730,10 @@
         <v>2337162273.491998</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>1.493622573568724</v>
       </c>
     </row>
     <row r="136">
@@ -2337,7 +2747,10 @@
         <v>3575994590.851601</v>
       </c>
       <c r="D136" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>1.823765039191863</v>
       </c>
     </row>
     <row r="137">
@@ -2351,7 +2764,10 @@
         <v>2629186769.761752</v>
       </c>
       <c r="D137" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>1.633540199811392</v>
       </c>
     </row>
     <row r="138">
@@ -2367,6 +2783,9 @@
       <c r="D138" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E138" s="2" t="n">
+        <v>1.516996442024495</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2379,7 +2798,10 @@
         <v>3969265368.709606</v>
       </c>
       <c r="D139" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>2.214901465708155</v>
       </c>
     </row>
     <row r="140">
@@ -2395,6 +2817,9 @@
       <c r="D140" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E140" s="2" t="n">
+        <v>1.972955803791078</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2409,6 +2834,9 @@
       <c r="D141" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E141" s="2" t="n">
+        <v>1.548285096065972</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2421,7 +2849,10 @@
         <v>2352618995.000783</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>1.587682863866854</v>
       </c>
     </row>
     <row r="143">
@@ -2437,6 +2868,9 @@
       <c r="D143" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E143" s="2" t="n">
+        <v>1.970545775668423</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2449,7 +2883,10 @@
         <v>2791139044.835035</v>
       </c>
       <c r="D144" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>1.800083964680445</v>
       </c>
     </row>
     <row r="145">
@@ -2463,7 +2900,10 @@
         <v>3764871352.905883</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>1.85313042846483</v>
       </c>
     </row>
     <row r="146">
@@ -2477,7 +2917,10 @@
         <v>2898237457.159917</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>1.660756453228978</v>
       </c>
     </row>
     <row r="147">
@@ -2491,7 +2934,10 @@
         <v>2319702669.910076</v>
       </c>
       <c r="D147" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>1.479589171769167</v>
       </c>
     </row>
     <row r="148">
@@ -2505,7 +2951,10 @@
         <v>3271199772.379237</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>1.807575567756445</v>
       </c>
     </row>
     <row r="149">
@@ -2519,7 +2968,10 @@
         <v>3253296504.873129</v>
       </c>
       <c r="D149" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>1.634412206707558</v>
       </c>
     </row>
     <row r="150">
@@ -2533,7 +2985,10 @@
         <v>3096982947.469305</v>
       </c>
       <c r="D150" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>1.744856864539137</v>
       </c>
     </row>
     <row r="151">
@@ -2547,7 +3002,10 @@
         <v>2962048363.707899</v>
       </c>
       <c r="D151" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>1.86581140513242</v>
       </c>
     </row>
     <row r="152">
@@ -2563,6 +3021,9 @@
       <c r="D152" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E152" s="2" t="n">
+        <v>1.534774380629702</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2575,7 +3036,10 @@
         <v>2433761439.749203</v>
       </c>
       <c r="D153" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>1.474531117744275</v>
       </c>
     </row>
     <row r="154">
@@ -2591,6 +3055,9 @@
       <c r="D154" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E154" s="2" t="n">
+        <v>1.800094603937485</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2605,6 +3072,9 @@
       <c r="D155" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E155" s="2" t="n">
+        <v>2.115493799869373</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2617,7 +3087,10 @@
         <v>3939161752.74195</v>
       </c>
       <c r="D156" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>2.147286784692504</v>
       </c>
     </row>
     <row r="157">
@@ -2631,7 +3104,10 @@
         <v>2575679806.788531</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>1.498634852087498</v>
       </c>
     </row>
     <row r="158">
@@ -2647,6 +3123,9 @@
       <c r="D158" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E158" s="2" t="n">
+        <v>1.67005535850736</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2659,7 +3138,10 @@
         <v>3478078465.287188</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>1.880979367844904</v>
       </c>
     </row>
     <row r="160">
@@ -2675,6 +3157,9 @@
       <c r="D160" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E160" s="2" t="n">
+        <v>1.910140108803492</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2687,7 +3172,10 @@
         <v>3908870735.686722</v>
       </c>
       <c r="D161" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>2.206325057682355</v>
       </c>
     </row>
     <row r="162">
@@ -2703,6 +3191,9 @@
       <c r="D162" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E162" s="2" t="n">
+        <v>1.54728828087785</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2717,6 +3208,9 @@
       <c r="D163" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E163" s="2" t="n">
+        <v>1.794470552817082</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2729,7 +3223,10 @@
         <v>2166303229.546304</v>
       </c>
       <c r="D164" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>1.292989490310327</v>
       </c>
     </row>
     <row r="165">
@@ -2745,6 +3242,9 @@
       <c r="D165" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E165" s="2" t="n">
+        <v>1.89426898544833</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2759,6 +3259,9 @@
       <c r="D166" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E166" s="2" t="n">
+        <v>1.782615032445373</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2771,7 +3274,10 @@
         <v>3359785933.41294</v>
       </c>
       <c r="D167" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>1.917943646148605</v>
       </c>
     </row>
     <row r="168">
@@ -2785,7 +3291,10 @@
         <v>2300503224.736649</v>
       </c>
       <c r="D168" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>1.543468153332487</v>
       </c>
     </row>
     <row r="169">
@@ -2799,7 +3308,10 @@
         <v>3911420712.895418</v>
       </c>
       <c r="D169" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>1.901023668939261</v>
       </c>
     </row>
     <row r="170">
@@ -2813,7 +3325,10 @@
         <v>3731525088.411994</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>2.021786972286384</v>
       </c>
     </row>
     <row r="171">
@@ -2827,7 +3342,10 @@
         <v>3145639549.049992</v>
       </c>
       <c r="D171" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>1.802041236204209</v>
       </c>
     </row>
     <row r="172">
@@ -2843,6 +3361,9 @@
       <c r="D172" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E172" s="2" t="n">
+        <v>2.02791260960557</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2855,7 +3376,10 @@
         <v>2522244997.733018</v>
       </c>
       <c r="D173" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>1.464277969275425</v>
       </c>
     </row>
     <row r="174">
@@ -2871,6 +3395,9 @@
       <c r="D174" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E174" s="2" t="n">
+        <v>1.645088888303022</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2885,6 +3412,9 @@
       <c r="D175" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E175" s="2" t="n">
+        <v>1.798405854853495</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2897,7 +3427,10 @@
         <v>3922272379.638346</v>
       </c>
       <c r="D176" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>2.2075491180457</v>
       </c>
     </row>
     <row r="177">
@@ -2911,7 +3444,10 @@
         <v>3924254682.560475</v>
       </c>
       <c r="D177" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>1.981700082452633</v>
       </c>
     </row>
     <row r="178">
@@ -2925,7 +3461,10 @@
         <v>3141899295.786462</v>
       </c>
       <c r="D178" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>1.81948804445146</v>
       </c>
     </row>
     <row r="179">
@@ -2939,7 +3478,10 @@
         <v>3391565090.206187</v>
       </c>
       <c r="D179" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>1.778299146445236</v>
       </c>
     </row>
     <row r="180">
@@ -2955,6 +3497,9 @@
       <c r="D180" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E180" s="2" t="n">
+        <v>2.098131136938411</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2967,7 +3512,10 @@
         <v>2429494379.886549</v>
       </c>
       <c r="D181" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>1.501081893412393</v>
       </c>
     </row>
     <row r="182">
@@ -2981,7 +3529,10 @@
         <v>3312047609.039018</v>
       </c>
       <c r="D182" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>1.716066314774165</v>
       </c>
     </row>
     <row r="183">
@@ -2995,7 +3546,10 @@
         <v>3071362230.74473</v>
       </c>
       <c r="D183" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>1.754994304249103</v>
       </c>
     </row>
     <row r="184">
@@ -3009,7 +3563,10 @@
         <v>2168450828.471925</v>
       </c>
       <c r="D184" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>1.596888207925692</v>
       </c>
     </row>
     <row r="185">
@@ -3025,6 +3582,9 @@
       <c r="D185" t="n">
         <v>0.9999</v>
       </c>
+      <c r="E185" s="2" t="n">
+        <v>1.372139945337449</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3037,7 +3597,10 @@
         <v>3121609333.920263</v>
       </c>
       <c r="D186" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>1.74283901501009</v>
       </c>
     </row>
     <row r="187">
@@ -3051,7 +3614,10 @@
         <v>2047725525.509593</v>
       </c>
       <c r="D187" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>1.51315731755018</v>
       </c>
     </row>
     <row r="188">
@@ -3065,7 +3631,10 @@
         <v>2094817954.902096</v>
       </c>
       <c r="D188" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>1.317763840221696</v>
       </c>
     </row>
     <row r="189">
@@ -3079,7 +3648,10 @@
         <v>2754997010.810349</v>
       </c>
       <c r="D189" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>1.501198872419368</v>
       </c>
     </row>
     <row r="190">
@@ -3093,7 +3665,10 @@
         <v>2280751215.766844</v>
       </c>
       <c r="D190" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>1.28108526665086</v>
       </c>
     </row>
     <row r="191">
@@ -3107,7 +3682,10 @@
         <v>2010953960.84398</v>
       </c>
       <c r="D191" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>1.190405750018393</v>
       </c>
     </row>
     <row r="192">
@@ -3121,7 +3699,10 @@
         <v>3758683799.965251</v>
       </c>
       <c r="D192" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>2.180661831750246</v>
       </c>
     </row>
     <row r="193">
@@ -3135,7 +3716,10 @@
         <v>3894930647.539765</v>
       </c>
       <c r="D193" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>2.047400164144567</v>
       </c>
     </row>
     <row r="194">
@@ -3149,7 +3733,10 @@
         <v>2195974339.209768</v>
       </c>
       <c r="D194" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>1.611416999816721</v>
       </c>
     </row>
     <row r="195">
@@ -3163,7 +3750,10 @@
         <v>2256043523.633725</v>
       </c>
       <c r="D195" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>1.436754966496076</v>
       </c>
     </row>
     <row r="196">
@@ -3177,7 +3767,10 @@
         <v>3597414659.881177</v>
       </c>
       <c r="D196" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>1.932453909561923</v>
       </c>
     </row>
     <row r="197">
@@ -3191,7 +3784,10 @@
         <v>2660817836.067347</v>
       </c>
       <c r="D197" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>1.696185973690684</v>
       </c>
     </row>
     <row r="198">
@@ -3205,7 +3801,10 @@
         <v>3676329430.370245</v>
       </c>
       <c r="D198" t="n">
-        <v>0.9</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>1.827860878659997</v>
       </c>
     </row>
     <row r="199">
@@ -3219,7 +3818,10 @@
         <v>3645267394.36131</v>
       </c>
       <c r="D199" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>2.134301022149859</v>
       </c>
     </row>
     <row r="200">
@@ -3233,7 +3835,10 @@
         <v>3023825148.069324</v>
       </c>
       <c r="D200" t="n">
-        <v>0.99</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>1.922173637709413</v>
       </c>
     </row>
     <row r="201">
@@ -3247,7 +3852,10 @@
         <v>3508397375.816388</v>
       </c>
       <c r="D201" t="n">
-        <v>0.999</v>
+        <v>0.9999</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>2.103524190189324</v>
       </c>
     </row>
   </sheetData>

--- a/data/task_parameters_evaluation.xlsx
+++ b/data/task_parameters_evaluation.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5.662996678308536</v>
+        <v>7.035190593044137</v>
       </c>
       <c r="C2" t="n">
-        <v>2041275211.227155</v>
+        <v>6853697444.629183</v>
       </c>
       <c r="D2" t="n">
-        <v>0.999</v>
+        <v>0.99179458115982</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>6.934746584869963</v>
+        <v>9.922521711255262</v>
       </c>
       <c r="C3" t="n">
-        <v>2688338482.293077</v>
+        <v>6434454845.610455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.999</v>
+        <v>0.9931665673165777</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>9.57515642366312</v>
+        <v>9.391330832452594</v>
       </c>
       <c r="C4" t="n">
-        <v>2203404767.48582</v>
+        <v>4902752266.537492</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999</v>
+        <v>0.9944967608763469</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7.830633241004661</v>
+        <v>8.493241421762118</v>
       </c>
       <c r="C5" t="n">
-        <v>3735694164.185751</v>
+        <v>4452347649.490882</v>
       </c>
       <c r="D5" t="n">
-        <v>0.999</v>
+        <v>0.9913795006866476</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>6.948133034682074</v>
+        <v>5.22020140790945</v>
       </c>
       <c r="C6" t="n">
-        <v>2240558336.643902</v>
+        <v>6328472189.432792</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9</v>
+        <v>0.9952746886960303</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>8.297325461549779</v>
+        <v>7.222906389564528</v>
       </c>
       <c r="C7" t="n">
-        <v>3203987703.924151</v>
+        <v>4234064577.448704</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9</v>
+        <v>0.9984731561412737</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>6.198463480157266</v>
+        <v>9.53114315242895</v>
       </c>
       <c r="C8" t="n">
-        <v>3433930626.273855</v>
+        <v>6315787031.440487</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.9989999109710989</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>6.96042089223903</v>
+        <v>5.557672264839849</v>
       </c>
       <c r="C9" t="n">
-        <v>3370273429.331845</v>
+        <v>6841880842.548573</v>
       </c>
       <c r="D9" t="n">
-        <v>0.99</v>
+        <v>0.9952398985640826</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>5.977398207811014</v>
+        <v>7.782827773165688</v>
       </c>
       <c r="C10" t="n">
-        <v>3212869000.763814</v>
+        <v>4897213049.535661</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999</v>
+        <v>0.9912565106494836</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>6.553330529404843</v>
+        <v>8.755781542828995</v>
       </c>
       <c r="C11" t="n">
-        <v>2759023509.556121</v>
+        <v>6607721217.685574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9</v>
+        <v>0.9905948889756749</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>9.837669013985309</v>
+        <v>6.475383545122529</v>
       </c>
       <c r="C12" t="n">
-        <v>3639926773.010654</v>
+        <v>7677075224.32688</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999</v>
+        <v>0.9931570660084674</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>8.558726743559294</v>
+        <v>7.741446822789014</v>
       </c>
       <c r="C13" t="n">
-        <v>2850747945.239495</v>
+        <v>4867919751.691654</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999</v>
+        <v>0.9934969980741033</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>5.02775854023147</v>
+        <v>7.742107349178273</v>
       </c>
       <c r="C14" t="n">
-        <v>3000400843.832637</v>
+        <v>7926176452.101929</v>
       </c>
       <c r="D14" t="n">
-        <v>0.99</v>
+        <v>0.9928266908276917</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>5.980188509284573</v>
+        <v>9.388821094136771</v>
       </c>
       <c r="C15" t="n">
-        <v>3280787914.51978</v>
+        <v>4201893362.09554</v>
       </c>
       <c r="D15" t="n">
-        <v>0.99</v>
+        <v>0.9937649807434589</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>5.728458854750012</v>
+        <v>7.433481292086514</v>
       </c>
       <c r="C16" t="n">
-        <v>3711528647.585059</v>
+        <v>7892955196.984865</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999</v>
+        <v>0.9963522523302563</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>9.449430795250247</v>
+        <v>9.456202813384731</v>
       </c>
       <c r="C17" t="n">
-        <v>3106420976.775494</v>
+        <v>5571582065.100415</v>
       </c>
       <c r="D17" t="n">
-        <v>0.999</v>
+        <v>0.9931596905413232</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>8.939792606571656</v>
+        <v>8.772557984172282</v>
       </c>
       <c r="C18" t="n">
-        <v>2076104034.388592</v>
+        <v>7083365947.60065</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9</v>
+        <v>0.9906060359439407</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>9.135768591784299</v>
+        <v>5.340845280439829</v>
       </c>
       <c r="C19" t="n">
-        <v>3473797094.482754</v>
+        <v>5441541903.365402</v>
       </c>
       <c r="D19" t="n">
-        <v>0.99</v>
+        <v>0.9983464433280004</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>5.375396312241319</v>
+        <v>7.019352917677226</v>
       </c>
       <c r="C20" t="n">
-        <v>2036043088.656366</v>
+        <v>6575397152.618835</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999</v>
+        <v>0.9909873731477835</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>5.523217206683926</v>
+        <v>5.873444306831069</v>
       </c>
       <c r="C21" t="n">
-        <v>2757864503.07458</v>
+        <v>6843444531.298059</v>
       </c>
       <c r="D21" t="n">
-        <v>0.99</v>
+        <v>0.9937550158064666</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>6.457134101567848</v>
+        <v>9.009719547095537</v>
       </c>
       <c r="C22" t="n">
-        <v>2389924317.528913</v>
+        <v>7141866387.336752</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999</v>
+        <v>0.9963510171586554</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>7.193823660493466</v>
+        <v>6.295787063107644</v>
       </c>
       <c r="C23" t="n">
-        <v>2032945606.508714</v>
+        <v>4628476619.22014</v>
       </c>
       <c r="D23" t="n">
-        <v>0.999</v>
+        <v>0.9904818659203473</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>6.791170179457382</v>
+        <v>5.434131962694935</v>
       </c>
       <c r="C24" t="n">
-        <v>2259665165.199902</v>
+        <v>6371442280.474825</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9999</v>
+        <v>0.9962329476027099</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>5.835354536183841</v>
+        <v>9.111068597989268</v>
       </c>
       <c r="C25" t="n">
-        <v>2817754637.235204</v>
+        <v>6224704198.485554</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9</v>
+        <v>0.9923392449030155</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>7.859058306008071</v>
+        <v>8.453086581188778</v>
       </c>
       <c r="C26" t="n">
-        <v>2416009056.58981</v>
+        <v>6424170436.941483</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9</v>
+        <v>0.9953848667910524</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>9.041206839833173</v>
+        <v>5.511272174839166</v>
       </c>
       <c r="C27" t="n">
-        <v>3839289861.506212</v>
+        <v>4493069610.229949</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9999</v>
+        <v>0.9931466458952611</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>6.561628659759453</v>
+        <v>5.973997831788505</v>
       </c>
       <c r="C28" t="n">
-        <v>3608988843.308181</v>
+        <v>7717842756.080981</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9</v>
+        <v>0.9922997816065769</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>7.617204269308933</v>
+        <v>7.776045508766938</v>
       </c>
       <c r="C29" t="n">
-        <v>3938892596.769102</v>
+        <v>7636919683.598009</v>
       </c>
       <c r="D29" t="n">
-        <v>0.99</v>
+        <v>0.9953160386541919</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>5.650853201497548</v>
+        <v>9.557546064822764</v>
       </c>
       <c r="C30" t="n">
-        <v>3969598583.566524</v>
+        <v>5942321116.371626</v>
       </c>
       <c r="D30" t="n">
-        <v>0.99</v>
+        <v>0.997201328174391</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>9.433470292635988</v>
+        <v>5.10440411656834</v>
       </c>
       <c r="C31" t="n">
-        <v>3740078425.248031</v>
+        <v>4177613744.591375</v>
       </c>
       <c r="D31" t="n">
-        <v>0.99</v>
+        <v>0.9969387136575348</v>
       </c>
     </row>
     <row r="32">
@@ -875,13 +875,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>8.559263164073792</v>
+        <v>6.991711459010578</v>
       </c>
       <c r="C32" t="n">
-        <v>3288703965.851254</v>
+        <v>4186848302.672344</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9999</v>
+        <v>0.9939817386247917</v>
       </c>
     </row>
     <row r="33">
@@ -889,13 +889,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>6.226322674160651</v>
+        <v>7.967457649058269</v>
       </c>
       <c r="C33" t="n">
-        <v>3874677962.653478</v>
+        <v>6286365407.642004</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9999</v>
+        <v>0.9900767055513148</v>
       </c>
     </row>
     <row r="34">
@@ -903,13 +903,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>6.184261579741684</v>
+        <v>9.930246636402746</v>
       </c>
       <c r="C34" t="n">
-        <v>3587128529.70233</v>
+        <v>7831165967.242574</v>
       </c>
       <c r="D34" t="n">
-        <v>0.99</v>
+        <v>0.9984417421085793</v>
       </c>
     </row>
     <row r="35">
@@ -917,13 +917,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7.954441681736775</v>
+        <v>5.488547160377244</v>
       </c>
       <c r="C35" t="n">
-        <v>2550785906.280042</v>
+        <v>4416710920.562597</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9999</v>
+        <v>0.9923701137529688</v>
       </c>
     </row>
     <row r="36">
@@ -931,13 +931,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>8.989368429787117</v>
+        <v>6.597813584317189</v>
       </c>
       <c r="C36" t="n">
-        <v>3067418057.144017</v>
+        <v>5679834031.711824</v>
       </c>
       <c r="D36" t="n">
-        <v>0.999</v>
+        <v>0.9979966135154598</v>
       </c>
     </row>
     <row r="37">
@@ -945,13 +945,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>6.88996346336233</v>
+        <v>5.464108550832939</v>
       </c>
       <c r="C37" t="n">
-        <v>3949892874.754253</v>
+        <v>7248568747.438648</v>
       </c>
       <c r="D37" t="n">
-        <v>0.99</v>
+        <v>0.9937344801945017</v>
       </c>
     </row>
     <row r="38">
@@ -959,13 +959,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>6.20059831376159</v>
+        <v>7.2165853125877</v>
       </c>
       <c r="C38" t="n">
-        <v>2556720489.318728</v>
+        <v>4789123976.596353</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9999</v>
+        <v>0.9921533999735472</v>
       </c>
     </row>
     <row r="39">
@@ -973,13 +973,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>7.809635425850978</v>
+        <v>9.426704634586784</v>
       </c>
       <c r="C39" t="n">
-        <v>3170684455.030489</v>
+        <v>5031458763.001301</v>
       </c>
       <c r="D39" t="n">
-        <v>0.99</v>
+        <v>0.9963896941772923</v>
       </c>
     </row>
     <row r="40">
@@ -987,13 +987,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>6.790193362807514</v>
+        <v>9.689680286138508</v>
       </c>
       <c r="C40" t="n">
-        <v>2700858981.362084</v>
+        <v>5996963783.258688</v>
       </c>
       <c r="D40" t="n">
-        <v>0.999</v>
+        <v>0.9961861746253393</v>
       </c>
     </row>
     <row r="41">
@@ -1001,13 +1001,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>5.060161821432336</v>
+        <v>8.841478833206663</v>
       </c>
       <c r="C41" t="n">
-        <v>3115899732.946083</v>
+        <v>6763246240.026827</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9</v>
+        <v>0.9938862856766403</v>
       </c>
     </row>
     <row r="42">
@@ -1015,13 +1015,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>6.201712270413927</v>
+        <v>6.403077142968979</v>
       </c>
       <c r="C42" t="n">
-        <v>2081015906.599709</v>
+        <v>6776671950.209902</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9999</v>
+        <v>0.9911481455272245</v>
       </c>
     </row>
     <row r="43">
@@ -1029,13 +1029,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>7.48370010222253</v>
+        <v>6.272870305629241</v>
       </c>
       <c r="C43" t="n">
-        <v>2623989209.005305</v>
+        <v>7938128427.325642</v>
       </c>
       <c r="D43" t="n">
-        <v>0.999</v>
+        <v>0.9907312621063152</v>
       </c>
     </row>
     <row r="44">
@@ -1043,13 +1043,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>8.181871452880136</v>
+        <v>5.30956545269682</v>
       </c>
       <c r="C44" t="n">
-        <v>2497732412.950726</v>
+        <v>4339429196.915135</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9999</v>
+        <v>0.9926677463692085</v>
       </c>
     </row>
     <row r="45">
@@ -1057,13 +1057,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>9.894431810705976</v>
+        <v>8.200086085199787</v>
       </c>
       <c r="C45" t="n">
-        <v>3082592611.553096</v>
+        <v>7091847150.514708</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9999</v>
+        <v>0.990439719006789</v>
       </c>
     </row>
     <row r="46">
@@ -1071,13 +1071,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>9.84565734840081</v>
+        <v>5.350775861064721</v>
       </c>
       <c r="C46" t="n">
-        <v>3193189099.733428</v>
+        <v>5150863595.275159</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9</v>
+        <v>0.99440512055764</v>
       </c>
     </row>
     <row r="47">
@@ -1085,13 +1085,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>7.424447859552025</v>
+        <v>7.27645351599256</v>
       </c>
       <c r="C47" t="n">
-        <v>3866736406.083718</v>
+        <v>5568956225.992663</v>
       </c>
       <c r="D47" t="n">
-        <v>0.999</v>
+        <v>0.991372654329148</v>
       </c>
     </row>
     <row r="48">
@@ -1099,13 +1099,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>9.82042276159355</v>
+        <v>6.260343886020788</v>
       </c>
       <c r="C48" t="n">
-        <v>3960544225.592988</v>
+        <v>5718853434.172337</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9</v>
+        <v>0.9911098040220466</v>
       </c>
     </row>
     <row r="49">
@@ -1113,13 +1113,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>9.821648577805249</v>
+        <v>9.931477400160535</v>
       </c>
       <c r="C49" t="n">
-        <v>2941202865.237553</v>
+        <v>7996430730.062279</v>
       </c>
       <c r="D49" t="n">
-        <v>0.999</v>
+        <v>0.990811259191111</v>
       </c>
     </row>
     <row r="50">
@@ -1127,13 +1127,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>7.507980308527412</v>
+        <v>7.765023415111838</v>
       </c>
       <c r="C50" t="n">
-        <v>2741993813.088811</v>
+        <v>4822840981.382071</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9999</v>
+        <v>0.9978374272283953</v>
       </c>
     </row>
     <row r="51">
@@ -1141,13 +1141,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>5.77377769302813</v>
+        <v>9.993943125561994</v>
       </c>
       <c r="C51" t="n">
-        <v>2973286231.659394</v>
+        <v>6686554329.14695</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9</v>
+        <v>0.9974666350511946</v>
       </c>
     </row>
     <row r="52">
@@ -1155,13 +1155,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>8.277420647584083</v>
+        <v>5.205283578480573</v>
       </c>
       <c r="C52" t="n">
-        <v>3902970550.117238</v>
+        <v>6354305829.458643</v>
       </c>
       <c r="D52" t="n">
-        <v>0.99</v>
+        <v>0.9933473088788953</v>
       </c>
     </row>
     <row r="53">
@@ -1169,13 +1169,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>9.392196004864148</v>
+        <v>9.029865176034944</v>
       </c>
       <c r="C53" t="n">
-        <v>2345241625.663661</v>
+        <v>6979781162.198751</v>
       </c>
       <c r="D53" t="n">
-        <v>0.99</v>
+        <v>0.9951965387890642</v>
       </c>
     </row>
     <row r="54">
@@ -1183,13 +1183,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>5.607625083703032</v>
+        <v>9.757567326063025</v>
       </c>
       <c r="C54" t="n">
-        <v>2372747480.491072</v>
+        <v>5263291601.745077</v>
       </c>
       <c r="D54" t="n">
-        <v>0.99</v>
+        <v>0.9980300566553765</v>
       </c>
     </row>
     <row r="55">
@@ -1197,13 +1197,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>5.762571890112357</v>
+        <v>8.990802390981791</v>
       </c>
       <c r="C55" t="n">
-        <v>2836101423.651895</v>
+        <v>7022403596.147123</v>
       </c>
       <c r="D55" t="n">
-        <v>0.999</v>
+        <v>0.9917552577423323</v>
       </c>
     </row>
     <row r="56">
@@ -1211,13 +1211,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>8.878853582452443</v>
+        <v>9.546756794897432</v>
       </c>
       <c r="C56" t="n">
-        <v>3861152071.530159</v>
+        <v>7711648537.820163</v>
       </c>
       <c r="D56" t="n">
-        <v>0.999</v>
+        <v>0.996782508096728</v>
       </c>
     </row>
     <row r="57">
@@ -1225,13 +1225,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>5.186316931079313</v>
+        <v>7.212101724366009</v>
       </c>
       <c r="C57" t="n">
-        <v>2418772594.572377</v>
+        <v>4378993323.150672</v>
       </c>
       <c r="D57" t="n">
-        <v>0.99</v>
+        <v>0.9938626876220277</v>
       </c>
     </row>
     <row r="58">
@@ -1239,13 +1239,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>7.209826266097405</v>
+        <v>8.270310083485109</v>
       </c>
       <c r="C58" t="n">
-        <v>2088500895.548698</v>
+        <v>7875362845.287735</v>
       </c>
       <c r="D58" t="n">
-        <v>0.99</v>
+        <v>0.9925361180529227</v>
       </c>
     </row>
     <row r="59">
@@ -1253,13 +1253,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>8.681510758920858</v>
+        <v>6.943404474968901</v>
       </c>
       <c r="C59" t="n">
-        <v>2253246986.167578</v>
+        <v>6594867353.157047</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9</v>
+        <v>0.9985368815190852</v>
       </c>
     </row>
     <row r="60">
@@ -1267,13 +1267,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>7.038682262918668</v>
+        <v>8.837492855113677</v>
       </c>
       <c r="C60" t="n">
-        <v>2595597787.905633</v>
+        <v>4134515049.724486</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9999</v>
+        <v>0.9912349161713585</v>
       </c>
     </row>
     <row r="61">
@@ -1281,13 +1281,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>7.799179677544926</v>
+        <v>5.236982780962493</v>
       </c>
       <c r="C61" t="n">
-        <v>2812269593.592202</v>
+        <v>7770164070.038912</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9999</v>
+        <v>0.9928359476371409</v>
       </c>
     </row>
     <row r="62">
@@ -1295,13 +1295,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>9.319921075572854</v>
+        <v>9.044078786344116</v>
       </c>
       <c r="C62" t="n">
-        <v>3826277235.99719</v>
+        <v>7550885243.519489</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9999</v>
+        <v>0.9979631771162006</v>
       </c>
     </row>
     <row r="63">
@@ -1309,13 +1309,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>7.772879452695494</v>
+        <v>7.686149358864952</v>
       </c>
       <c r="C63" t="n">
-        <v>2581108563.41969</v>
+        <v>7902797997.364389</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9999</v>
+        <v>0.9939882266223283</v>
       </c>
     </row>
     <row r="64">
@@ -1323,13 +1323,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>9.358566469534704</v>
+        <v>7.739656872264028</v>
       </c>
       <c r="C64" t="n">
-        <v>2796502420.509092</v>
+        <v>6330816694.354734</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9999</v>
+        <v>0.9958461855827033</v>
       </c>
     </row>
     <row r="65">
@@ -1337,13 +1337,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>8.957534452301031</v>
+        <v>9.219205524210953</v>
       </c>
       <c r="C65" t="n">
-        <v>2730221501.577714</v>
+        <v>6522238272.395544</v>
       </c>
       <c r="D65" t="n">
-        <v>0.99</v>
+        <v>0.9908507802780024</v>
       </c>
     </row>
     <row r="66">
@@ -1351,13 +1351,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>5.506834961082902</v>
+        <v>9.266607036078227</v>
       </c>
       <c r="C66" t="n">
-        <v>3855127516.843309</v>
+        <v>4309825804.578824</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9</v>
+        <v>0.9934951099733865</v>
       </c>
     </row>
     <row r="67">
@@ -1365,13 +1365,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>6.794097040679503</v>
+        <v>9.500899903190763</v>
       </c>
       <c r="C67" t="n">
-        <v>2602167972.519974</v>
+        <v>7516492502.817214</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9</v>
+        <v>0.9969316457388762</v>
       </c>
     </row>
     <row r="68">
@@ -1379,13 +1379,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>6.040411115495745</v>
+        <v>7.69900917118535</v>
       </c>
       <c r="C68" t="n">
-        <v>3928084983.064842</v>
+        <v>4763055329.462688</v>
       </c>
       <c r="D68" t="n">
-        <v>0.99</v>
+        <v>0.9986392245355293</v>
       </c>
     </row>
     <row r="69">
@@ -1393,13 +1393,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>9.641488666250531</v>
+        <v>5.27251774278821</v>
       </c>
       <c r="C69" t="n">
-        <v>2533516845.2327</v>
+        <v>6174861718.093123</v>
       </c>
       <c r="D69" t="n">
-        <v>0.99</v>
+        <v>0.990177535080412</v>
       </c>
     </row>
     <row r="70">
@@ -1407,13 +1407,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>9.853842994059804</v>
+        <v>7.349549969819369</v>
       </c>
       <c r="C70" t="n">
-        <v>3774709127.327841</v>
+        <v>4054876510.548213</v>
       </c>
       <c r="D70" t="n">
-        <v>0.999</v>
+        <v>0.9958658686632368</v>
       </c>
     </row>
     <row r="71">
@@ -1421,13 +1421,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>8.020365660718619</v>
+        <v>8.368769026497223</v>
       </c>
       <c r="C71" t="n">
-        <v>2359585041.053266</v>
+        <v>4589101102.473661</v>
       </c>
       <c r="D71" t="n">
-        <v>0.99</v>
+        <v>0.9966691014147633</v>
       </c>
     </row>
     <row r="72">
@@ -1435,13 +1435,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>5.423139582333053</v>
+        <v>5.307877948709078</v>
       </c>
       <c r="C72" t="n">
-        <v>3899067911.866893</v>
+        <v>5053205210.664603</v>
       </c>
       <c r="D72" t="n">
-        <v>0.999</v>
+        <v>0.9966582931960452</v>
       </c>
     </row>
     <row r="73">
@@ -1449,13 +1449,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>5.071335982192617</v>
+        <v>6.54960049442801</v>
       </c>
       <c r="C73" t="n">
-        <v>2127937253.108463</v>
+        <v>7495803656.293126</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9</v>
+        <v>0.9953009168855845</v>
       </c>
     </row>
     <row r="74">
@@ -1463,13 +1463,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>7.062618863539202</v>
+        <v>7.059964554133282</v>
       </c>
       <c r="C74" t="n">
-        <v>3482278841.347547</v>
+        <v>4635270919.233545</v>
       </c>
       <c r="D74" t="n">
-        <v>0.99</v>
+        <v>0.9917857086908637</v>
       </c>
     </row>
     <row r="75">
@@ -1477,13 +1477,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>8.864275511896812</v>
+        <v>8.778815931998775</v>
       </c>
       <c r="C75" t="n">
-        <v>2892749333.815838</v>
+        <v>6271616724.311706</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9</v>
+        <v>0.992743612459318</v>
       </c>
     </row>
     <row r="76">
@@ -1491,13 +1491,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>5.773437874803044</v>
+        <v>5.310284530901249</v>
       </c>
       <c r="C76" t="n">
-        <v>2346973041.075265</v>
+        <v>4536436562.380282</v>
       </c>
       <c r="D76" t="n">
-        <v>0.999</v>
+        <v>0.9979714678738059</v>
       </c>
     </row>
     <row r="77">
@@ -1505,13 +1505,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>6.637261253836789</v>
+        <v>7.917738564185218</v>
       </c>
       <c r="C77" t="n">
-        <v>2591009511.21867</v>
+        <v>5032160379.719085</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9999</v>
+        <v>0.9958064451970458</v>
       </c>
     </row>
     <row r="78">
@@ -1519,13 +1519,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>9.134283428823146</v>
+        <v>6.302424472062365</v>
       </c>
       <c r="C78" t="n">
-        <v>3161460799.323009</v>
+        <v>5993885511.982898</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9</v>
+        <v>0.9919341434507245</v>
       </c>
     </row>
     <row r="79">
@@ -1533,13 +1533,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>5.100649122647743</v>
+        <v>9.091533876747226</v>
       </c>
       <c r="C79" t="n">
-        <v>3283967896.512748</v>
+        <v>5030480317.958164</v>
       </c>
       <c r="D79" t="n">
-        <v>0.99</v>
+        <v>0.9955595349323622</v>
       </c>
     </row>
     <row r="80">
@@ -1547,13 +1547,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>5.954222579723933</v>
+        <v>8.923022141265722</v>
       </c>
       <c r="C80" t="n">
-        <v>3477113285.259815</v>
+        <v>7740596932.440762</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9999</v>
+        <v>0.9913859810350991</v>
       </c>
     </row>
     <row r="81">
@@ -1561,13 +1561,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>7.333560944406281</v>
+        <v>5.37617526558522</v>
       </c>
       <c r="C81" t="n">
-        <v>2485695439.738623</v>
+        <v>4623924364.290057</v>
       </c>
       <c r="D81" t="n">
-        <v>0.999</v>
+        <v>0.9922925454682017</v>
       </c>
     </row>
     <row r="82">
@@ -1575,13 +1575,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>5.476691071375097</v>
+        <v>5.569129364264183</v>
       </c>
       <c r="C82" t="n">
-        <v>3852423964.901986</v>
+        <v>5495525340.365761</v>
       </c>
       <c r="D82" t="n">
-        <v>0.999</v>
+        <v>0.9979627265287733</v>
       </c>
     </row>
     <row r="83">
@@ -1589,13 +1589,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>7.511429282096248</v>
+        <v>9.78969537822152</v>
       </c>
       <c r="C83" t="n">
-        <v>3235750182.18655</v>
+        <v>7930895887.044041</v>
       </c>
       <c r="D83" t="n">
-        <v>0.99</v>
+        <v>0.9965707786449535</v>
       </c>
     </row>
     <row r="84">
@@ -1603,13 +1603,13 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>5.737330750087351</v>
+        <v>8.741087990020471</v>
       </c>
       <c r="C84" t="n">
-        <v>3785343841.910222</v>
+        <v>6236601533.431965</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9999</v>
+        <v>0.9900221929912176</v>
       </c>
     </row>
     <row r="85">
@@ -1617,13 +1617,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>8.385313346191296</v>
+        <v>6.009236436692126</v>
       </c>
       <c r="C85" t="n">
-        <v>3335866694.237963</v>
+        <v>7196598369.124186</v>
       </c>
       <c r="D85" t="n">
-        <v>0.999</v>
+        <v>0.9986222834523579</v>
       </c>
     </row>
     <row r="86">
@@ -1631,13 +1631,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>6.876305314188144</v>
+        <v>9.02528475768802</v>
       </c>
       <c r="C86" t="n">
-        <v>3683014462.820036</v>
+        <v>6411279560.986396</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9999</v>
+        <v>0.9943178197178287</v>
       </c>
     </row>
     <row r="87">
@@ -1645,13 +1645,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>8.682392834850489</v>
+        <v>9.171399130393539</v>
       </c>
       <c r="C87" t="n">
-        <v>2113214330.753854</v>
+        <v>4272688503.09702</v>
       </c>
       <c r="D87" t="n">
-        <v>0.9</v>
+        <v>0.9908071601181926</v>
       </c>
     </row>
     <row r="88">
@@ -1659,13 +1659,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>9.531305358935807</v>
+        <v>9.342854334448687</v>
       </c>
       <c r="C88" t="n">
-        <v>3209167710.603492</v>
+        <v>7483519088.210688</v>
       </c>
       <c r="D88" t="n">
-        <v>0.99</v>
+        <v>0.9977833738753332</v>
       </c>
     </row>
     <row r="89">
@@ -1673,13 +1673,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>7.618810578153383</v>
+        <v>7.171524850501998</v>
       </c>
       <c r="C89" t="n">
-        <v>3801089956.409418</v>
+        <v>4950514126.339977</v>
       </c>
       <c r="D89" t="n">
-        <v>0.999</v>
+        <v>0.9940056478761763</v>
       </c>
     </row>
     <row r="90">
@@ -1687,13 +1687,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>8.860750433709352</v>
+        <v>6.023840409116058</v>
       </c>
       <c r="C90" t="n">
-        <v>2236294207.577805</v>
+        <v>6986365595.959855</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9</v>
+        <v>0.9933819716134481</v>
       </c>
     </row>
     <row r="91">
@@ -1701,13 +1701,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>7.192586577095136</v>
+        <v>5.431526702369684</v>
       </c>
       <c r="C91" t="n">
-        <v>2422377709.491845</v>
+        <v>6195357437.398148</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9</v>
+        <v>0.9904427756181954</v>
       </c>
     </row>
     <row r="92">
@@ -1715,13 +1715,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>5.212535645731624</v>
+        <v>9.785448965299903</v>
       </c>
       <c r="C92" t="n">
-        <v>2965331653.814487</v>
+        <v>4966359259.687761</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9999</v>
+        <v>0.9985833091094508</v>
       </c>
     </row>
     <row r="93">
@@ -1729,13 +1729,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>7.047870276338123</v>
+        <v>6.014890023401051</v>
       </c>
       <c r="C93" t="n">
-        <v>3309687214.528853</v>
+        <v>5963212119.292833</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9</v>
+        <v>0.9921617787773072</v>
       </c>
     </row>
     <row r="94">
@@ -1743,13 +1743,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>6.317204956216321</v>
+        <v>7.68836670419664</v>
       </c>
       <c r="C94" t="n">
-        <v>3308736348.364349</v>
+        <v>5862213082.109648</v>
       </c>
       <c r="D94" t="n">
-        <v>0.999</v>
+        <v>0.9977355672458029</v>
       </c>
     </row>
     <row r="95">
@@ -1757,13 +1757,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>6.223590750203218</v>
+        <v>5.941502016154912</v>
       </c>
       <c r="C95" t="n">
-        <v>2092759319.255111</v>
+        <v>4557921916.605024</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9</v>
+        <v>0.9905961342864348</v>
       </c>
     </row>
     <row r="96">
@@ -1771,13 +1771,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>8.933800990309258</v>
+        <v>5.866149830685946</v>
       </c>
       <c r="C96" t="n">
-        <v>3921042689.211942</v>
+        <v>4027550049.069485</v>
       </c>
       <c r="D96" t="n">
-        <v>0.99</v>
+        <v>0.9929006244122413</v>
       </c>
     </row>
     <row r="97">
@@ -1785,13 +1785,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>9.93753644259913</v>
+        <v>6.833559715927573</v>
       </c>
       <c r="C97" t="n">
-        <v>2420997728.23853</v>
+        <v>4466848974.138222</v>
       </c>
       <c r="D97" t="n">
-        <v>0.99</v>
+        <v>0.9936606454843228</v>
       </c>
     </row>
     <row r="98">
@@ -1799,13 +1799,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>6.531980065306724</v>
+        <v>5.606747136818044</v>
       </c>
       <c r="C98" t="n">
-        <v>3535795734.941409</v>
+        <v>4781156311.409361</v>
       </c>
       <c r="D98" t="n">
-        <v>0.99</v>
+        <v>0.9931807634674052</v>
       </c>
     </row>
     <row r="99">
@@ -1813,13 +1813,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>6.086825609080392</v>
+        <v>7.531660486830745</v>
       </c>
       <c r="C99" t="n">
-        <v>2086605745.023101</v>
+        <v>4677942044.871375</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9999</v>
+        <v>0.9986335569188781</v>
       </c>
     </row>
     <row r="100">
@@ -1827,13 +1827,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>8.676454889201713</v>
+        <v>8.026397278552817</v>
       </c>
       <c r="C100" t="n">
-        <v>3194775178.475915</v>
+        <v>5523767645.751068</v>
       </c>
       <c r="D100" t="n">
-        <v>0.99</v>
+        <v>0.9955394015163521</v>
       </c>
     </row>
     <row r="101">
@@ -1841,13 +1841,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>9.331837192866423</v>
+        <v>5.815463538432542</v>
       </c>
       <c r="C101" t="n">
-        <v>2819719150.514021</v>
+        <v>5333107526.72397</v>
       </c>
       <c r="D101" t="n">
-        <v>0.999</v>
+        <v>0.9944845441450837</v>
       </c>
     </row>
     <row r="102">
@@ -1855,13 +1855,13 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>8.854420884138056</v>
+        <v>9.55700904817372</v>
       </c>
       <c r="C102" t="n">
-        <v>3414472444.419219</v>
+        <v>5565884568.288736</v>
       </c>
       <c r="D102" t="n">
-        <v>0.99</v>
+        <v>0.9925922985471166</v>
       </c>
     </row>
     <row r="103">
@@ -1869,13 +1869,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>7.515591010486511</v>
+        <v>9.708697371718557</v>
       </c>
       <c r="C103" t="n">
-        <v>2920630632.222028</v>
+        <v>7697756524.978447</v>
       </c>
       <c r="D103" t="n">
-        <v>0.999</v>
+        <v>0.9989417710796772</v>
       </c>
     </row>
     <row r="104">
@@ -1883,13 +1883,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>5.965855373508452</v>
+        <v>5.187023908919091</v>
       </c>
       <c r="C104" t="n">
-        <v>3002702931.952337</v>
+        <v>4377666827.331114</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9999</v>
+        <v>0.9943007136016625</v>
       </c>
     </row>
     <row r="105">
@@ -1897,13 +1897,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>7.714583692303524</v>
+        <v>6.865101922716088</v>
       </c>
       <c r="C105" t="n">
-        <v>3659499961.458301</v>
+        <v>5492770081.440395</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9999</v>
+        <v>0.9915800846770534</v>
       </c>
     </row>
     <row r="106">
@@ -1911,13 +1911,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>9.759955919288128</v>
+        <v>8.337757928247957</v>
       </c>
       <c r="C106" t="n">
-        <v>3527924884.487551</v>
+        <v>4444464689.457505</v>
       </c>
       <c r="D106" t="n">
-        <v>0.999</v>
+        <v>0.9957526380881139</v>
       </c>
     </row>
     <row r="107">
@@ -1925,13 +1925,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>8.765478589612465</v>
+        <v>7.300361505813433</v>
       </c>
       <c r="C107" t="n">
-        <v>2763976252.105522</v>
+        <v>7876279205.092436</v>
       </c>
       <c r="D107" t="n">
-        <v>0.9</v>
+        <v>0.9937282937010029</v>
       </c>
     </row>
     <row r="108">
@@ -1939,13 +1939,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>9.700123566268346</v>
+        <v>5.646457506776557</v>
       </c>
       <c r="C108" t="n">
-        <v>3999209986.049125</v>
+        <v>4727294220.795474</v>
       </c>
       <c r="D108" t="n">
-        <v>0.999</v>
+        <v>0.9985951719398087</v>
       </c>
     </row>
     <row r="109">
@@ -1953,13 +1953,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>6.455982073168022</v>
+        <v>8.334638237727569</v>
       </c>
       <c r="C109" t="n">
-        <v>3205551078.694489</v>
+        <v>6456912870.405828</v>
       </c>
       <c r="D109" t="n">
-        <v>0.999</v>
+        <v>0.9978231052562461</v>
       </c>
     </row>
     <row r="110">
@@ -1967,13 +1967,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>7.949506374835217</v>
+        <v>9.534307868954865</v>
       </c>
       <c r="C110" t="n">
-        <v>2585096918.062966</v>
+        <v>7533802504.709238</v>
       </c>
       <c r="D110" t="n">
-        <v>0.999</v>
+        <v>0.9948977571181431</v>
       </c>
     </row>
     <row r="111">
@@ -1981,13 +1981,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>5.36953659145887</v>
+        <v>7.421323484950269</v>
       </c>
       <c r="C111" t="n">
-        <v>2393678082.645704</v>
+        <v>4465168978.884188</v>
       </c>
       <c r="D111" t="n">
-        <v>0.9</v>
+        <v>0.992313236597551</v>
       </c>
     </row>
     <row r="112">
@@ -1995,13 +1995,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>5.182411707529574</v>
+        <v>9.192302887179505</v>
       </c>
       <c r="C112" t="n">
-        <v>2767864578.589826</v>
+        <v>6686509444.591964</v>
       </c>
       <c r="D112" t="n">
-        <v>0.999</v>
+        <v>0.9950484809461089</v>
       </c>
     </row>
     <row r="113">
@@ -2009,13 +2009,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>7.248581356798459</v>
+        <v>5.066535181054624</v>
       </c>
       <c r="C113" t="n">
-        <v>3387798895.469378</v>
+        <v>5751422249.160532</v>
       </c>
       <c r="D113" t="n">
-        <v>0.99</v>
+        <v>0.9977829738704759</v>
       </c>
     </row>
     <row r="114">
@@ -2023,13 +2023,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>6.284801997244228</v>
+        <v>6.98815637797161</v>
       </c>
       <c r="C114" t="n">
-        <v>2025297281.129525</v>
+        <v>5993931721.034147</v>
       </c>
       <c r="D114" t="n">
-        <v>0.9</v>
+        <v>0.9988456374891937</v>
       </c>
     </row>
     <row r="115">
@@ -2037,13 +2037,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>8.67142394245983</v>
+        <v>7.302898177588331</v>
       </c>
       <c r="C115" t="n">
-        <v>2579645465.053738</v>
+        <v>7773600828.798568</v>
       </c>
       <c r="D115" t="n">
-        <v>0.999</v>
+        <v>0.9949109752434102</v>
       </c>
     </row>
     <row r="116">
@@ -2051,13 +2051,13 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>7.517230369335895</v>
+        <v>7.536977020285322</v>
       </c>
       <c r="C116" t="n">
-        <v>2004418537.201465</v>
+        <v>6853312996.294353</v>
       </c>
       <c r="D116" t="n">
-        <v>0.999</v>
+        <v>0.9927491857995712</v>
       </c>
     </row>
     <row r="117">
@@ -2065,13 +2065,13 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>9.771233344567799</v>
+        <v>5.40805648620874</v>
       </c>
       <c r="C117" t="n">
-        <v>3537859880.039716</v>
+        <v>7542145969.081491</v>
       </c>
       <c r="D117" t="n">
-        <v>0.9999</v>
+        <v>0.9975489336970147</v>
       </c>
     </row>
     <row r="118">
@@ -2079,13 +2079,13 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>6.495034898705534</v>
+        <v>6.938443509027494</v>
       </c>
       <c r="C118" t="n">
-        <v>3469743412.611381</v>
+        <v>5870738133.838884</v>
       </c>
       <c r="D118" t="n">
-        <v>0.99</v>
+        <v>0.9962454544033374</v>
       </c>
     </row>
     <row r="119">
@@ -2093,13 +2093,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>7.538654331550612</v>
+        <v>5.862878418472929</v>
       </c>
       <c r="C119" t="n">
-        <v>2458950775.974457</v>
+        <v>6549542105.022329</v>
       </c>
       <c r="D119" t="n">
-        <v>0.999</v>
+        <v>0.9915243786199147</v>
       </c>
     </row>
     <row r="120">
@@ -2107,13 +2107,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>5.931002335795605</v>
+        <v>9.48626830457356</v>
       </c>
       <c r="C120" t="n">
-        <v>2020288733.561071</v>
+        <v>4806331648.901916</v>
       </c>
       <c r="D120" t="n">
-        <v>0.99</v>
+        <v>0.9949475293913669</v>
       </c>
     </row>
     <row r="121">
@@ -2121,13 +2121,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>5.056805143634855</v>
+        <v>8.325868098015338</v>
       </c>
       <c r="C121" t="n">
-        <v>2848164988.481399</v>
+        <v>6342538734.130838</v>
       </c>
       <c r="D121" t="n">
-        <v>0.99</v>
+        <v>0.9933772037401589</v>
       </c>
     </row>
     <row r="122">
@@ -2135,13 +2135,13 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>9.566458643242793</v>
+        <v>8.888932418117772</v>
       </c>
       <c r="C122" t="n">
-        <v>2394584221.064873</v>
+        <v>6683275016.002554</v>
       </c>
       <c r="D122" t="n">
-        <v>0.9</v>
+        <v>0.9987873123955437</v>
       </c>
     </row>
     <row r="123">
@@ -2149,13 +2149,13 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>7.599494686069336</v>
+        <v>8.826973601655453</v>
       </c>
       <c r="C123" t="n">
-        <v>3991646225.108678</v>
+        <v>7405684815.844595</v>
       </c>
       <c r="D123" t="n">
-        <v>0.99</v>
+        <v>0.9975020696111008</v>
       </c>
     </row>
     <row r="124">
@@ -2163,13 +2163,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>7.680460829010335</v>
+        <v>5.972829914656256</v>
       </c>
       <c r="C124" t="n">
-        <v>2755172614.819665</v>
+        <v>7918062661.116781</v>
       </c>
       <c r="D124" t="n">
-        <v>0.9</v>
+        <v>0.9975842110886819</v>
       </c>
     </row>
     <row r="125">
@@ -2177,13 +2177,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>9.118362063116772</v>
+        <v>7.10339414583826</v>
       </c>
       <c r="C125" t="n">
-        <v>2370857459.087273</v>
+        <v>6283385718.056521</v>
       </c>
       <c r="D125" t="n">
-        <v>0.99</v>
+        <v>0.991209863465253</v>
       </c>
     </row>
     <row r="126">
@@ -2191,13 +2191,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>6.718238604788663</v>
+        <v>7.686272457903902</v>
       </c>
       <c r="C126" t="n">
-        <v>3310425410.805653</v>
+        <v>5500801943.589329</v>
       </c>
       <c r="D126" t="n">
-        <v>0.99</v>
+        <v>0.9960899127059081</v>
       </c>
     </row>
     <row r="127">
@@ -2205,13 +2205,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>9.342447963803604</v>
+        <v>9.346790562027365</v>
       </c>
       <c r="C127" t="n">
-        <v>2873735111.565702</v>
+        <v>6775902461.329448</v>
       </c>
       <c r="D127" t="n">
-        <v>0.99</v>
+        <v>0.9914597123345855</v>
       </c>
     </row>
     <row r="128">
@@ -2219,13 +2219,13 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>7.878210745685638</v>
+        <v>8.775834607189523</v>
       </c>
       <c r="C128" t="n">
-        <v>2321662348.21428</v>
+        <v>4119518110.685133</v>
       </c>
       <c r="D128" t="n">
-        <v>0.9</v>
+        <v>0.9928393497386422</v>
       </c>
     </row>
     <row r="129">
@@ -2233,13 +2233,13 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>9.094392195284206</v>
+        <v>6.065462429541812</v>
       </c>
       <c r="C129" t="n">
-        <v>3734997915.934702</v>
+        <v>4049254947.562927</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9999</v>
+        <v>0.9972813515135787</v>
       </c>
     </row>
     <row r="130">
@@ -2247,13 +2247,13 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>8.849305886631315</v>
+        <v>7.094110631976436</v>
       </c>
       <c r="C130" t="n">
-        <v>2389056610.993787</v>
+        <v>5976136802.949015</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9</v>
+        <v>0.9956217222700456</v>
       </c>
     </row>
     <row r="131">
@@ -2261,13 +2261,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>9.424847261070543</v>
+        <v>9.926581546937689</v>
       </c>
       <c r="C131" t="n">
-        <v>3507113404.174014</v>
+        <v>6553167368.172138</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9</v>
+        <v>0.9980771782723382</v>
       </c>
     </row>
     <row r="132">
@@ -2275,13 +2275,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>5.610823464646014</v>
+        <v>9.567546611975398</v>
       </c>
       <c r="C132" t="n">
-        <v>2910820153.873046</v>
+        <v>6827454607.064733</v>
       </c>
       <c r="D132" t="n">
-        <v>0.9</v>
+        <v>0.9972429897670692</v>
       </c>
     </row>
     <row r="133">
@@ -2289,13 +2289,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>6.394941865800003</v>
+        <v>8.017429998902539</v>
       </c>
       <c r="C133" t="n">
-        <v>3300905436.361066</v>
+        <v>7226382883.183594</v>
       </c>
       <c r="D133" t="n">
-        <v>0.999</v>
+        <v>0.9931845165647298</v>
       </c>
     </row>
     <row r="134">
@@ -2303,13 +2303,13 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>8.022644085371336</v>
+        <v>6.622382502517901</v>
       </c>
       <c r="C134" t="n">
-        <v>3732455624.680674</v>
+        <v>5555297059.025564</v>
       </c>
       <c r="D134" t="n">
-        <v>0.999</v>
+        <v>0.996091051650532</v>
       </c>
     </row>
     <row r="135">
@@ -2317,13 +2317,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>7.816782014339521</v>
+        <v>7.205795651657091</v>
       </c>
       <c r="C135" t="n">
-        <v>2337162273.491998</v>
+        <v>6770277413.167352</v>
       </c>
       <c r="D135" t="n">
-        <v>0.9</v>
+        <v>0.9986702532580723</v>
       </c>
     </row>
     <row r="136">
@@ -2331,13 +2331,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>6.101000157680669</v>
+        <v>8.591722879061528</v>
       </c>
       <c r="C136" t="n">
-        <v>3575994590.851601</v>
+        <v>7858581742.754637</v>
       </c>
       <c r="D136" t="n">
-        <v>0.999</v>
+        <v>0.9921566562768483</v>
       </c>
     </row>
     <row r="137">
@@ -2345,13 +2345,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>8.200561253705281</v>
+        <v>7.076067403786147</v>
       </c>
       <c r="C137" t="n">
-        <v>2629186769.761752</v>
+        <v>5903482837.878127</v>
       </c>
       <c r="D137" t="n">
-        <v>0.99</v>
+        <v>0.9932086427386038</v>
       </c>
     </row>
     <row r="138">
@@ -2359,13 +2359,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>5.54732768961261</v>
+        <v>8.364121555603109</v>
       </c>
       <c r="C138" t="n">
-        <v>2875378696.474491</v>
+        <v>4999505827.291789</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9999</v>
+        <v>0.9985558500368008</v>
       </c>
     </row>
     <row r="139">
@@ -2373,13 +2373,13 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>9.191035277135235</v>
+        <v>9.199001947701728</v>
       </c>
       <c r="C139" t="n">
-        <v>3969265368.709606</v>
+        <v>5044992978.929379</v>
       </c>
       <c r="D139" t="n">
-        <v>0.999</v>
+        <v>0.9985755479038421</v>
       </c>
     </row>
     <row r="140">
@@ -2387,13 +2387,13 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>9.87944987340385</v>
+        <v>7.731488116816052</v>
       </c>
       <c r="C140" t="n">
-        <v>3180723954.275926</v>
+        <v>5811378070.783687</v>
       </c>
       <c r="D140" t="n">
-        <v>0.9999</v>
+        <v>0.9944174646739242</v>
       </c>
     </row>
     <row r="141">
@@ -2401,13 +2401,13 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>8.489362524352748</v>
+        <v>7.288061417432962</v>
       </c>
       <c r="C141" t="n">
-        <v>2341631581.290956</v>
+        <v>7814846045.905311</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9999</v>
+        <v>0.9917861650083938</v>
       </c>
     </row>
     <row r="142">
@@ -2415,13 +2415,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>8.937093513897301</v>
+        <v>9.314352767515771</v>
       </c>
       <c r="C142" t="n">
-        <v>2352618995.000783</v>
+        <v>4840142085.021288</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9</v>
+        <v>0.997547242347398</v>
       </c>
     </row>
     <row r="143">
@@ -2429,13 +2429,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>8.334191465650084</v>
+        <v>8.368738615806864</v>
       </c>
       <c r="C143" t="n">
-        <v>3498403508.258072</v>
+        <v>5584382716.596367</v>
       </c>
       <c r="D143" t="n">
-        <v>0.9999</v>
+        <v>0.9977378263690505</v>
       </c>
     </row>
     <row r="144">
@@ -2443,13 +2443,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>9.542506241693111</v>
+        <v>6.168462402805271</v>
       </c>
       <c r="C144" t="n">
-        <v>2791139044.835035</v>
+        <v>6101746813.429819</v>
       </c>
       <c r="D144" t="n">
-        <v>0.999</v>
+        <v>0.9972191053575316</v>
       </c>
     </row>
     <row r="145">
@@ -2457,13 +2457,13 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>5.573220273729865</v>
+        <v>5.685308973738119</v>
       </c>
       <c r="C145" t="n">
-        <v>3764871352.905883</v>
+        <v>4360948819.847395</v>
       </c>
       <c r="D145" t="n">
-        <v>0.9</v>
+        <v>0.9956161859004573</v>
       </c>
     </row>
     <row r="146">
@@ -2471,13 +2471,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>7.263238582829572</v>
+        <v>7.271726694458273</v>
       </c>
       <c r="C146" t="n">
-        <v>2898237457.159917</v>
+        <v>7202590631.970901</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9</v>
+        <v>0.9920263530190337</v>
       </c>
     </row>
     <row r="147">
@@ -2485,13 +2485,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>7.721886767168597</v>
+        <v>7.175967136944763</v>
       </c>
       <c r="C147" t="n">
-        <v>2319702669.910076</v>
+        <v>5159015219.048707</v>
       </c>
       <c r="D147" t="n">
-        <v>0.999</v>
+        <v>0.9987918765091037</v>
       </c>
     </row>
     <row r="148">
@@ -2499,13 +2499,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>7.348722096049807</v>
+        <v>5.656436444779821</v>
       </c>
       <c r="C148" t="n">
-        <v>3271199772.379237</v>
+        <v>4437381246.15399</v>
       </c>
       <c r="D148" t="n">
-        <v>0.9</v>
+        <v>0.9941251889435584</v>
       </c>
     </row>
     <row r="149">
@@ -2513,13 +2513,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>5.235935790873921</v>
+        <v>7.636914551532136</v>
       </c>
       <c r="C149" t="n">
-        <v>3253296504.873129</v>
+        <v>6860857680.585702</v>
       </c>
       <c r="D149" t="n">
-        <v>0.9</v>
+        <v>0.9930490939901336</v>
       </c>
     </row>
     <row r="150">
@@ -2527,13 +2527,13 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>7.383215609083218</v>
+        <v>7.962154675124225</v>
       </c>
       <c r="C150" t="n">
-        <v>3096982947.469305</v>
+        <v>5360236872.360468</v>
       </c>
       <c r="D150" t="n">
-        <v>0.999</v>
+        <v>0.9976032469198102</v>
       </c>
     </row>
     <row r="151">
@@ -2541,13 +2541,13 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>9.561975709941713</v>
+        <v>9.662313942193467</v>
       </c>
       <c r="C151" t="n">
-        <v>2962048363.707899</v>
+        <v>7400360435.586209</v>
       </c>
       <c r="D151" t="n">
-        <v>0.999</v>
+        <v>0.9981786763893973</v>
       </c>
     </row>
     <row r="152">
@@ -2555,13 +2555,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>8.783684066274695</v>
+        <v>9.403955785346859</v>
       </c>
       <c r="C152" t="n">
-        <v>2243930882.082296</v>
+        <v>6641698382.440477</v>
       </c>
       <c r="D152" t="n">
-        <v>0.9999</v>
+        <v>0.9914113930799565</v>
       </c>
     </row>
     <row r="153">
@@ -2569,13 +2569,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>7.113858320287951</v>
+        <v>5.155596897149045</v>
       </c>
       <c r="C153" t="n">
-        <v>2433761439.749203</v>
+        <v>5371441419.51472</v>
       </c>
       <c r="D153" t="n">
-        <v>0.999</v>
+        <v>0.9904738201232757</v>
       </c>
     </row>
     <row r="154">
@@ -2583,13 +2583,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>5.51165984730045</v>
+        <v>5.072286084105117</v>
       </c>
       <c r="C154" t="n">
-        <v>3636580178.222839</v>
+        <v>5052668026.757341</v>
       </c>
       <c r="D154" t="n">
-        <v>0.9999</v>
+        <v>0.9974384948240195</v>
       </c>
     </row>
     <row r="155">
@@ -2597,13 +2597,13 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>8.349484920008285</v>
+        <v>8.727636810309928</v>
       </c>
       <c r="C155" t="n">
-        <v>3881105600.247569</v>
+        <v>4911297081.380102</v>
       </c>
       <c r="D155" t="n">
-        <v>0.9999</v>
+        <v>0.9987952229715769</v>
       </c>
     </row>
     <row r="156">
@@ -2611,13 +2611,13 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>8.476261094694122</v>
+        <v>7.070340148312716</v>
       </c>
       <c r="C156" t="n">
-        <v>3939161752.74195</v>
+        <v>4195847998.891266</v>
       </c>
       <c r="D156" t="n">
-        <v>0.99</v>
+        <v>0.9989348161801468</v>
       </c>
     </row>
     <row r="157">
@@ -2625,13 +2625,13 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>6.743179714687894</v>
+        <v>7.364936577135461</v>
       </c>
       <c r="C157" t="n">
-        <v>2575679806.788531</v>
+        <v>4557195977.65926</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9</v>
+        <v>0.9906414666530665</v>
       </c>
     </row>
     <row r="158">
@@ -2639,13 +2639,13 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>7.809160726455841</v>
+        <v>8.315156651858112</v>
       </c>
       <c r="C158" t="n">
-        <v>2808495446.791623</v>
+        <v>4268407704.28401</v>
       </c>
       <c r="D158" t="n">
-        <v>0.9999</v>
+        <v>0.9950082850868585</v>
       </c>
     </row>
     <row r="159">
@@ -2653,13 +2653,13 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>7.294137297724353</v>
+        <v>9.691621641222238</v>
       </c>
       <c r="C159" t="n">
-        <v>3478078465.287188</v>
+        <v>5242762103.84629</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9</v>
+        <v>0.9914663800236556</v>
       </c>
     </row>
     <row r="160">
@@ -2667,13 +2667,13 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>7.713426330930996</v>
+        <v>6.971949931540418</v>
       </c>
       <c r="C160" t="n">
-        <v>3467776111.252016</v>
+        <v>7667920927.886604</v>
       </c>
       <c r="D160" t="n">
-        <v>0.9999</v>
+        <v>0.9939818938569268</v>
       </c>
     </row>
     <row r="161">
@@ -2681,13 +2681,13 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>9.370121538389078</v>
+        <v>8.445843875753864</v>
       </c>
       <c r="C161" t="n">
-        <v>3908870735.686722</v>
+        <v>5611153443.225717</v>
       </c>
       <c r="D161" t="n">
-        <v>0.999</v>
+        <v>0.9932258592903446</v>
       </c>
     </row>
     <row r="162">
@@ -2695,13 +2695,13 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>5.867575711269144</v>
+        <v>8.176462265228773</v>
       </c>
       <c r="C162" t="n">
-        <v>2888860224.061131</v>
+        <v>4232136474.445598</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9999</v>
+        <v>0.9935216887477932</v>
       </c>
     </row>
     <row r="163">
@@ -2709,13 +2709,13 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>7.598874770936579</v>
+        <v>6.274016192095269</v>
       </c>
       <c r="C163" t="n">
-        <v>3183843003.152452</v>
+        <v>5521577864.395492</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9999</v>
+        <v>0.9947142212904646</v>
       </c>
     </row>
     <row r="164">
@@ -2723,13 +2723,13 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>6.084571537553613</v>
+        <v>6.680990057461045</v>
       </c>
       <c r="C164" t="n">
-        <v>2166303229.546304</v>
+        <v>4179712085.074069</v>
       </c>
       <c r="D164" t="n">
-        <v>0.99</v>
+        <v>0.990871872343547</v>
       </c>
     </row>
     <row r="165">
@@ -2737,13 +2737,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>8.636257614984107</v>
+        <v>7.923412086635461</v>
       </c>
       <c r="C165" t="n">
-        <v>3231970065.276051</v>
+        <v>6913039009.388355</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9999</v>
+        <v>0.9914423553147669</v>
       </c>
     </row>
     <row r="166">
@@ -2751,13 +2751,13 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>6.146573381762737</v>
+        <v>5.660487748652003</v>
       </c>
       <c r="C166" t="n">
-        <v>3456878459.851658</v>
+        <v>4667936282.874227</v>
       </c>
       <c r="D166" t="n">
-        <v>0.9999</v>
+        <v>0.9917253478768575</v>
       </c>
     </row>
     <row r="167">
@@ -2765,13 +2765,13 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>8.327371668757642</v>
+        <v>8.017670627090029</v>
       </c>
       <c r="C167" t="n">
-        <v>3359785933.41294</v>
+        <v>6025243905.307129</v>
       </c>
       <c r="D167" t="n">
-        <v>0.9</v>
+        <v>0.9957115433064271</v>
       </c>
     </row>
     <row r="168">
@@ -2779,13 +2779,13 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>8.624311950442753</v>
+        <v>7.395724810773944</v>
       </c>
       <c r="C168" t="n">
-        <v>2300503224.736649</v>
+        <v>7008055173.170885</v>
       </c>
       <c r="D168" t="n">
-        <v>0.99</v>
+        <v>0.9917611559784357</v>
       </c>
     </row>
     <row r="169">
@@ -2793,13 +2793,13 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>5.48244713295558</v>
+        <v>8.954563312128045</v>
       </c>
       <c r="C169" t="n">
-        <v>3911420712.895418</v>
+        <v>5976083845.346441</v>
       </c>
       <c r="D169" t="n">
-        <v>0.9</v>
+        <v>0.9957243276192499</v>
       </c>
     </row>
     <row r="170">
@@ -2807,13 +2807,13 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>7.873149543398464</v>
+        <v>6.829732615868251</v>
       </c>
       <c r="C170" t="n">
-        <v>3731525088.411994</v>
+        <v>7806791332.01128</v>
       </c>
       <c r="D170" t="n">
-        <v>0.9</v>
+        <v>0.9931044503615291</v>
       </c>
     </row>
     <row r="171">
@@ -2821,13 +2821,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>7.877127904465733</v>
+        <v>8.586247059809292</v>
       </c>
       <c r="C171" t="n">
-        <v>3145639549.049992</v>
+        <v>4405658521.560506</v>
       </c>
       <c r="D171" t="n">
-        <v>0.9</v>
+        <v>0.9926836674161237</v>
       </c>
     </row>
     <row r="172">
@@ -2835,13 +2835,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>6.962844980444306</v>
+        <v>9.364180616220427</v>
       </c>
       <c r="C172" t="n">
-        <v>3938757446.598295</v>
+        <v>5711159062.847222</v>
       </c>
       <c r="D172" t="n">
-        <v>0.9999</v>
+        <v>0.9941248066206703</v>
       </c>
     </row>
     <row r="173">
@@ -2849,13 +2849,13 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>6.56182312852469</v>
+        <v>5.149177907378556</v>
       </c>
       <c r="C173" t="n">
-        <v>2522244997.733018</v>
+        <v>7622879451.137333</v>
       </c>
       <c r="D173" t="n">
-        <v>0.9</v>
+        <v>0.9986735459250676</v>
       </c>
     </row>
     <row r="174">
@@ -2863,13 +2863,13 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>9.10708816182705</v>
+        <v>5.56131468388496</v>
       </c>
       <c r="C174" t="n">
-        <v>2469802853.07224</v>
+        <v>7807306014.643341</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9999</v>
+        <v>0.993296348551822</v>
       </c>
     </row>
     <row r="175">
@@ -2877,13 +2877,13 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>9.964183993301885</v>
+        <v>5.900611840576936</v>
       </c>
       <c r="C175" t="n">
-        <v>2698230322.504913</v>
+        <v>7084410446.189474</v>
       </c>
       <c r="D175" t="n">
-        <v>0.9999</v>
+        <v>0.9912748589314909</v>
       </c>
     </row>
     <row r="176">
@@ -2891,13 +2891,13 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>9.321762102442536</v>
+        <v>7.190192307440203</v>
       </c>
       <c r="C176" t="n">
-        <v>3922272379.638346</v>
+        <v>7895262086.404416</v>
       </c>
       <c r="D176" t="n">
-        <v>0.9</v>
+        <v>0.996496468795419</v>
       </c>
     </row>
     <row r="177">
@@ -2905,13 +2905,13 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>6.445367827304329</v>
+        <v>6.670592091722687</v>
       </c>
       <c r="C177" t="n">
-        <v>3924254682.560475</v>
+        <v>7529722579.092563</v>
       </c>
       <c r="D177" t="n">
-        <v>0.9</v>
+        <v>0.990950190011594</v>
       </c>
     </row>
     <row r="178">
@@ -2919,13 +2919,13 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>8.116432027048425</v>
+        <v>5.86897281196142</v>
       </c>
       <c r="C178" t="n">
-        <v>3141899295.786462</v>
+        <v>5887850355.10653</v>
       </c>
       <c r="D178" t="n">
-        <v>0.99</v>
+        <v>0.9955253714889795</v>
       </c>
     </row>
     <row r="179">
@@ -2933,13 +2933,13 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>6.403195056018463</v>
+        <v>8.865552003522268</v>
       </c>
       <c r="C179" t="n">
-        <v>3391565090.206187</v>
+        <v>7340868548.133976</v>
       </c>
       <c r="D179" t="n">
-        <v>0.999</v>
+        <v>0.9948799949621384</v>
       </c>
     </row>
     <row r="180">
@@ -2947,13 +2947,13 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>9.666230365836086</v>
+        <v>6.114414165288645</v>
       </c>
       <c r="C180" t="n">
-        <v>3558710575.474564</v>
+        <v>4927094784.542953</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9999</v>
+        <v>0.9923219406380606</v>
       </c>
     </row>
     <row r="181">
@@ -2961,13 +2961,13 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>7.471240580425153</v>
+        <v>5.812434291105885</v>
       </c>
       <c r="C181" t="n">
-        <v>2429494379.886549</v>
+        <v>6579624143.054382</v>
       </c>
       <c r="D181" t="n">
-        <v>0.999</v>
+        <v>0.9936896177187566</v>
       </c>
     </row>
     <row r="182">
@@ -2975,13 +2975,13 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>5.992338955038253</v>
+        <v>6.972942848166605</v>
       </c>
       <c r="C182" t="n">
-        <v>3312047609.039018</v>
+        <v>6233843302.913078</v>
       </c>
       <c r="D182" t="n">
-        <v>0.99</v>
+        <v>0.9947151672064761</v>
       </c>
     </row>
     <row r="183">
@@ -2989,13 +2989,13 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>7.634058046714678</v>
+        <v>9.418467537901357</v>
       </c>
       <c r="C183" t="n">
-        <v>3071362230.74473</v>
+        <v>6375492277.806891</v>
       </c>
       <c r="D183" t="n">
-        <v>0.99</v>
+        <v>0.9956674391413458</v>
       </c>
     </row>
     <row r="184">
@@ -3003,13 +3003,13 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>9.932042753272246</v>
+        <v>9.178730662267979</v>
       </c>
       <c r="C184" t="n">
-        <v>2168450828.471925</v>
+        <v>7407388439.443706</v>
       </c>
       <c r="D184" t="n">
-        <v>0.999</v>
+        <v>0.9901228682373781</v>
       </c>
     </row>
     <row r="185">
@@ -3017,13 +3017,13 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>5.251444232958472</v>
+        <v>9.461031149348077</v>
       </c>
       <c r="C185" t="n">
-        <v>2551770056.967639</v>
+        <v>7469398307.596281</v>
       </c>
       <c r="D185" t="n">
-        <v>0.9999</v>
+        <v>0.9933883982878666</v>
       </c>
     </row>
     <row r="186">
@@ -3031,13 +3031,13 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>7.240184665724438</v>
+        <v>7.523978581953857</v>
       </c>
       <c r="C186" t="n">
-        <v>3121609333.920263</v>
+        <v>4244195279.918229</v>
       </c>
       <c r="D186" t="n">
-        <v>0.999</v>
+        <v>0.9984917536236446</v>
       </c>
     </row>
     <row r="187">
@@ -3045,13 +3045,13 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>9.444763752969507</v>
+        <v>7.608168205353684</v>
       </c>
       <c r="C187" t="n">
-        <v>2047725525.509593</v>
+        <v>4882905506.359959</v>
       </c>
       <c r="D187" t="n">
-        <v>0.999</v>
+        <v>0.9914733648975831</v>
       </c>
     </row>
     <row r="188">
@@ -3059,13 +3059,13 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>6.739893668201628</v>
+        <v>5.275023338711361</v>
       </c>
       <c r="C188" t="n">
-        <v>2094817954.902096</v>
+        <v>5099132200.7203</v>
       </c>
       <c r="D188" t="n">
-        <v>0.999</v>
+        <v>0.9919176606383618</v>
       </c>
     </row>
     <row r="189">
@@ -3073,13 +3073,13 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>5.92076049786708</v>
+        <v>8.542506813904119</v>
       </c>
       <c r="C189" t="n">
-        <v>2754997010.810349</v>
+        <v>6326051637.685852</v>
       </c>
       <c r="D189" t="n">
-        <v>0.9</v>
+        <v>0.991991342972994</v>
       </c>
     </row>
     <row r="190">
@@ -3087,13 +3087,13 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>5.387781606894188</v>
+        <v>6.010174234900587</v>
       </c>
       <c r="C190" t="n">
-        <v>2280751215.766844</v>
+        <v>5110671222.11776</v>
       </c>
       <c r="D190" t="n">
-        <v>0.99</v>
+        <v>0.9970172370609973</v>
       </c>
     </row>
     <row r="191">
@@ -3101,13 +3101,13 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>5.523056908103191</v>
+        <v>7.914964223663494</v>
       </c>
       <c r="C191" t="n">
-        <v>2010953960.84398</v>
+        <v>6153440656.451368</v>
       </c>
       <c r="D191" t="n">
-        <v>0.99</v>
+        <v>0.9922483900315382</v>
       </c>
     </row>
     <row r="192">
@@ -3115,13 +3115,13 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>9.760427587612066</v>
+        <v>5.197654812190275</v>
       </c>
       <c r="C192" t="n">
-        <v>3758683799.965251</v>
+        <v>6645064430.004534</v>
       </c>
       <c r="D192" t="n">
-        <v>0.9</v>
+        <v>0.9973774968517006</v>
       </c>
     </row>
     <row r="193">
@@ -3129,13 +3129,13 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>7.419183241991977</v>
+        <v>5.761890933431034</v>
       </c>
       <c r="C193" t="n">
-        <v>3894930647.539765</v>
+        <v>7832069406.247749</v>
       </c>
       <c r="D193" t="n">
-        <v>0.99</v>
+        <v>0.9962528391520687</v>
       </c>
     </row>
     <row r="194">
@@ -3143,13 +3143,13 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>9.985242780869459</v>
+        <v>8.917323287901437</v>
       </c>
       <c r="C194" t="n">
-        <v>2195974339.209768</v>
+        <v>5958330966.070971</v>
       </c>
       <c r="D194" t="n">
-        <v>0.99</v>
+        <v>0.9979772741928706</v>
       </c>
     </row>
     <row r="195">
@@ -3157,13 +3157,13 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>7.481667129286762</v>
+        <v>5.459158864990281</v>
       </c>
       <c r="C195" t="n">
-        <v>2256043523.633725</v>
+        <v>5646337372.856369</v>
       </c>
       <c r="D195" t="n">
-        <v>0.99</v>
+        <v>0.9920136383318401</v>
       </c>
     </row>
     <row r="196">
@@ -3171,13 +3171,13 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>7.378575173006013</v>
+        <v>6.68395456877529</v>
       </c>
       <c r="C196" t="n">
-        <v>3597414659.881177</v>
+        <v>7293553445.798521</v>
       </c>
       <c r="D196" t="n">
-        <v>0.999</v>
+        <v>0.9912486811661482</v>
       </c>
     </row>
     <row r="197">
@@ -3185,13 +3185,13 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>8.84497705949499</v>
+        <v>7.376788756548322</v>
       </c>
       <c r="C197" t="n">
-        <v>2660817836.067347</v>
+        <v>6447022533.156588</v>
       </c>
       <c r="D197" t="n">
-        <v>0.999</v>
+        <v>0.9901053134603915</v>
       </c>
     </row>
     <row r="198">
@@ -3199,13 +3199,13 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>5.674606221140627</v>
+        <v>7.037185259325598</v>
       </c>
       <c r="C198" t="n">
-        <v>3676329430.370245</v>
+        <v>7122986402.795731</v>
       </c>
       <c r="D198" t="n">
-        <v>0.9</v>
+        <v>0.9944654976852665</v>
       </c>
     </row>
     <row r="199">
@@ -3213,13 +3213,13 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>9.712678791110495</v>
+        <v>7.026855971783602</v>
       </c>
       <c r="C199" t="n">
-        <v>3645267394.36131</v>
+        <v>5721196815.173933</v>
       </c>
       <c r="D199" t="n">
-        <v>0.999</v>
+        <v>0.9957258152081089</v>
       </c>
     </row>
     <row r="200">
@@ -3227,13 +3227,13 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>9.982895955534421</v>
+        <v>9.923935135325733</v>
       </c>
       <c r="C200" t="n">
-        <v>3023825148.069324</v>
+        <v>4527843613.699435</v>
       </c>
       <c r="D200" t="n">
-        <v>0.99</v>
+        <v>0.9933376774667226</v>
       </c>
     </row>
     <row r="201">
@@ -3241,13 +3241,13 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>9.974578610043086</v>
+        <v>7.699817237515535</v>
       </c>
       <c r="C201" t="n">
-        <v>3508397375.816388</v>
+        <v>7965882898.259705</v>
       </c>
       <c r="D201" t="n">
-        <v>0.999</v>
+        <v>0.9969376724907869</v>
       </c>
     </row>
   </sheetData>
